--- a/Vac Report Template.xlsx
+++ b/Vac Report Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\General\Desktop\Dev Files\Reports_Generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2663A4-A1DD-4CEE-B097-762C99384365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E631CE-673E-4EF7-9728-FC3E38FD0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,29 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t>Class Teacher: Mr Mugoni</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="75">
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>MUKOMBORERO NYASHA</t>
-  </si>
-  <si>
-    <t>GUZHA TANAKA</t>
-  </si>
-  <si>
-    <t>MUPAKA TRISH</t>
-  </si>
-  <si>
-    <t>CHABOKA ANNY</t>
-  </si>
-  <si>
-    <t>GARWE TINASHE</t>
-  </si>
-  <si>
     <t>Test 1</t>
   </si>
   <si>
@@ -63,24 +45,9 @@
     <t>Test 5</t>
   </si>
   <si>
-    <t>Average</t>
-  </si>
-  <si>
     <t>Final</t>
   </si>
   <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Mr Mugoni</t>
-  </si>
-  <si>
-    <t>Biology</t>
-  </si>
-  <si>
-    <t>U6Scie</t>
-  </si>
-  <si>
     <t>Month/Year:</t>
   </si>
   <si>
@@ -90,7 +57,199 @@
     <t xml:space="preserve">Class: </t>
   </si>
   <si>
-    <t>April 2026</t>
+    <t>CHADENGA JOSHBETH</t>
+  </si>
+  <si>
+    <t>CHIKEREMA OLIVER</t>
+  </si>
+  <si>
+    <t>CHINYUNDO NATALIE</t>
+  </si>
+  <si>
+    <t>CHIRAPA OBRIAN</t>
+  </si>
+  <si>
+    <t>DZVAIRO MDUDUZI</t>
+  </si>
+  <si>
+    <t>GOTORA LEONARD</t>
+  </si>
+  <si>
+    <t>GWENGI ELSY</t>
+  </si>
+  <si>
+    <t>HURUDZA KAKU</t>
+  </si>
+  <si>
+    <t>JOZI DENZEL</t>
+  </si>
+  <si>
+    <t>KATSANDE VALERY</t>
+  </si>
+  <si>
+    <t>KATSUWA ANTONY</t>
+  </si>
+  <si>
+    <t>KAPITO WAYNE</t>
+  </si>
+  <si>
+    <t>KUFA VESTER</t>
+  </si>
+  <si>
+    <t>KUPFUMA HARZEL</t>
+  </si>
+  <si>
+    <t>MAERESERA TINOTENDA</t>
+  </si>
+  <si>
+    <t>MAFUTA ANASHE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAFUTA CARLON </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAKHAYA TINOTENDA </t>
+  </si>
+  <si>
+    <t>MAKOMBERO AARON</t>
+  </si>
+  <si>
+    <t>MAKONI VONGAI</t>
+  </si>
+  <si>
+    <t>MAMBWERERE DARLINE</t>
+  </si>
+  <si>
+    <t>MANDENGU RUMBIDZAI R</t>
+  </si>
+  <si>
+    <t>MANDISHONA SHALOM</t>
+  </si>
+  <si>
+    <t>MANHAMBARA NADIA</t>
+  </si>
+  <si>
+    <t>MANHANZWA TINASHE</t>
+  </si>
+  <si>
+    <t>MANYORE GIFT</t>
+  </si>
+  <si>
+    <t>MARIRA EMMANUEL</t>
+  </si>
+  <si>
+    <t>MARURU TAKUDZWA</t>
+  </si>
+  <si>
+    <t>MARUTAWANA TIARA</t>
+  </si>
+  <si>
+    <t>MASAMVU TERRY</t>
+  </si>
+  <si>
+    <t>MATEO PRAYER</t>
+  </si>
+  <si>
+    <t>MATIKITI BRADLEY</t>
+  </si>
+  <si>
+    <t>MATOPE ALEWNDRA</t>
+  </si>
+  <si>
+    <t>MAVERENGE SAMANTHA</t>
+  </si>
+  <si>
+    <t>MAVESERE TADIWANASHE</t>
+  </si>
+  <si>
+    <t>MHANDO KING</t>
+  </si>
+  <si>
+    <t>MOMBESHORA TINASHE</t>
+  </si>
+  <si>
+    <t>MPOFU PRINCE</t>
+  </si>
+  <si>
+    <t>MUDZIMU NICOLLETTE</t>
+  </si>
+  <si>
+    <t>MUGONDA SHALOM</t>
+  </si>
+  <si>
+    <t>MUJIWA MOREBLESSING</t>
+  </si>
+  <si>
+    <t>MUKUMBIRA TANATSWA</t>
+  </si>
+  <si>
+    <t>MUKUNGWA CHIEF</t>
+  </si>
+  <si>
+    <t>MUPAKWE MELODY</t>
+  </si>
+  <si>
+    <t>MUPUNWA PREVIOUS</t>
+  </si>
+  <si>
+    <t>MUSHANJE VALLERY</t>
+  </si>
+  <si>
+    <t>MUSHATI WILLARD</t>
+  </si>
+  <si>
+    <t>MUSWE LYANNE</t>
+  </si>
+  <si>
+    <t>MUTASA ADONIS</t>
+  </si>
+  <si>
+    <t>MUTIMUDYE MIRIAM</t>
+  </si>
+  <si>
+    <t>NYABOCHO KUNASHE</t>
+  </si>
+  <si>
+    <t>NYAMAPFENE MAKANAKA</t>
+  </si>
+  <si>
+    <t>NYAMUTORA KUNASHE</t>
+  </si>
+  <si>
+    <t>ROJAS ASHLEY</t>
+  </si>
+  <si>
+    <t>SERIMA ORLAPH</t>
+  </si>
+  <si>
+    <t>SIGAUKE JOAN</t>
+  </si>
+  <si>
+    <t>SIGAUKE MAZVITA</t>
+  </si>
+  <si>
+    <t>ZINDOGA FADZAI</t>
+  </si>
+  <si>
+    <t>O Level</t>
+  </si>
+  <si>
+    <t>Aug 2026</t>
+  </si>
+  <si>
+    <t>test 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total </t>
+  </si>
+  <si>
+    <t>Mr Chilwa</t>
+  </si>
+  <si>
+    <t>Mathematics</t>
+  </si>
+  <si>
+    <t>Class Teacher:</t>
   </si>
 </sst>
 </file>
@@ -126,9 +285,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -415,244 +573,2396 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="31.90625" customWidth="1"/>
-    <col min="8" max="8" width="10.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>1</v>
       </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <f>(H7/$H$65)*100</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="G6" t="s">
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8">
         <v>12</v>
       </c>
-      <c r="H6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="H8">
+        <v>12</v>
+      </c>
+      <c r="I8">
+        <f>(H8/$H$65)*100</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>9</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9">
         <v>2</v>
       </c>
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <v>11</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <f>AVERAGE(B7:F7)</f>
-        <v>6.8</v>
-      </c>
-      <c r="H7" s="1">
-        <f>(G7/$G$12)*100</f>
-        <v>62.962962962962955</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>15</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
-      <c r="F8">
-        <v>7</v>
-      </c>
-      <c r="G8">
-        <f t="shared" ref="G8:G12" si="0">AVERAGE(B8:F8)</f>
-        <v>6.2</v>
-      </c>
-      <c r="H8" s="1">
-        <f t="shared" ref="H8:H12" si="1">(G8/$G$12)*100</f>
-        <v>57.407407407407405</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>10</v>
-      </c>
-      <c r="E9">
-        <v>3</v>
-      </c>
       <c r="F9">
         <v>7</v>
       </c>
       <c r="G9">
-        <f t="shared" si="0"/>
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="H9" s="1">
-        <f t="shared" si="1"/>
-        <v>42.592592592592588</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+      <c r="H9">
+        <v>13</v>
+      </c>
+      <c r="I9">
+        <f>(H9/$H$65)*100</f>
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G10">
-        <f t="shared" si="0"/>
-        <v>5.2</v>
-      </c>
-      <c r="H10" s="1">
-        <f t="shared" si="1"/>
-        <v>48.148148148148145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="H10">
+        <v>12</v>
+      </c>
+      <c r="I10">
+        <f>(H10/$H$65)*100</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D11">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E11">
         <v>2</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G11">
-        <f t="shared" si="0"/>
-        <v>7.2</v>
-      </c>
-      <c r="H11" s="1">
-        <f t="shared" si="1"/>
-        <v>66.666666666666657</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+      <c r="H11">
+        <v>14</v>
+      </c>
+      <c r="I11">
+        <f>(H11/$H$65)*100</f>
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12">
         <v>10</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12">
+        <v>7</v>
+      </c>
+      <c r="G12">
+        <v>15</v>
+      </c>
+      <c r="H12">
+        <v>15</v>
+      </c>
+      <c r="I12">
+        <f>(H12/$H$65)*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>7</v>
+      </c>
+      <c r="G13">
+        <v>15</v>
+      </c>
+      <c r="H13">
+        <v>15</v>
+      </c>
+      <c r="I13">
+        <f>(H13/$H$65)*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14">
+        <v>9</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="F14">
+        <v>7</v>
+      </c>
+      <c r="G14">
+        <v>13</v>
+      </c>
+      <c r="H14">
+        <v>13</v>
+      </c>
+      <c r="I14">
+        <f>(H14/$H$65)*100</f>
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15">
+        <v>8</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+      <c r="D15">
+        <v>6</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="F15">
+        <v>7</v>
+      </c>
+      <c r="G15">
+        <v>14</v>
+      </c>
+      <c r="H15">
+        <v>14</v>
+      </c>
+      <c r="I15">
+        <f>(H15/$H$65)*100</f>
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>9</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16">
+        <v>7</v>
+      </c>
+      <c r="G16">
+        <v>14</v>
+      </c>
+      <c r="H16">
+        <v>14</v>
+      </c>
+      <c r="I16">
+        <f>(H16/$H$65)*100</f>
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>20</v>
       </c>
-      <c r="E12">
-        <v>5</v>
-      </c>
-      <c r="F12">
+      <c r="B17">
+        <v>10</v>
+      </c>
+      <c r="C17">
+        <v>8</v>
+      </c>
+      <c r="D17">
+        <v>5</v>
+      </c>
+      <c r="E17">
+        <v>5</v>
+      </c>
+      <c r="F17">
+        <v>7</v>
+      </c>
+      <c r="G17">
+        <v>16</v>
+      </c>
+      <c r="H17">
+        <v>16</v>
+      </c>
+      <c r="I17">
+        <f>(H17/$H$65)*100</f>
+        <v>106.66666666666667</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <v>7</v>
+      </c>
+      <c r="D18">
+        <v>8</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>7</v>
+      </c>
+      <c r="G18">
         <v>12</v>
       </c>
-      <c r="G12">
-        <f t="shared" si="0"/>
-        <v>10.8</v>
-      </c>
-      <c r="H12" s="1">
-        <f t="shared" si="1"/>
+      <c r="H18">
+        <v>12</v>
+      </c>
+      <c r="I18">
+        <f>(H18/$H$65)*100</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19">
+        <v>8</v>
+      </c>
+      <c r="C19">
+        <v>9</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19">
+        <v>7</v>
+      </c>
+      <c r="G19">
+        <v>12</v>
+      </c>
+      <c r="H19">
+        <v>12</v>
+      </c>
+      <c r="I19">
+        <f>(H19/$H$65)*100</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
+        <v>10</v>
+      </c>
+      <c r="C20">
+        <v>10</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20">
+        <v>7</v>
+      </c>
+      <c r="G20">
+        <v>16</v>
+      </c>
+      <c r="H20">
+        <v>16</v>
+      </c>
+      <c r="I20">
+        <f>(H20/$H$65)*100</f>
+        <v>106.66666666666667</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21">
+        <v>10</v>
+      </c>
+      <c r="C21">
+        <v>10</v>
+      </c>
+      <c r="D21">
+        <v>9</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21">
+        <v>7</v>
+      </c>
+      <c r="G21">
+        <v>17</v>
+      </c>
+      <c r="H21">
+        <v>17</v>
+      </c>
+      <c r="I21">
+        <f>(H21/$H$65)*100</f>
+        <v>113.33333333333333</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22">
+        <v>10</v>
+      </c>
+      <c r="C22">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <v>7</v>
+      </c>
+      <c r="G22">
+        <v>14</v>
+      </c>
+      <c r="H22">
+        <v>14</v>
+      </c>
+      <c r="I22">
+        <f>(H22/$H$65)*100</f>
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>9</v>
+      </c>
+      <c r="D23">
+        <v>8</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <v>7</v>
+      </c>
+      <c r="G23">
+        <v>13</v>
+      </c>
+      <c r="H23">
+        <v>13</v>
+      </c>
+      <c r="I23">
+        <f>(H23/$H$65)*100</f>
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24">
+        <v>10</v>
+      </c>
+      <c r="C24">
+        <v>7</v>
+      </c>
+      <c r="D24">
+        <v>6</v>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24">
+        <v>7</v>
+      </c>
+      <c r="G24">
+        <v>16</v>
+      </c>
+      <c r="H24">
+        <v>16</v>
+      </c>
+      <c r="I24">
+        <f>(H24/$H$65)*100</f>
+        <v>106.66666666666667</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25">
+        <v>10</v>
+      </c>
+      <c r="C25">
+        <v>9</v>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+      <c r="E25">
+        <v>5</v>
+      </c>
+      <c r="F25">
+        <v>7</v>
+      </c>
+      <c r="G25">
+        <v>14</v>
+      </c>
+      <c r="H25">
+        <v>14</v>
+      </c>
+      <c r="I25">
+        <f>(H25/$H$65)*100</f>
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26">
+        <v>9</v>
+      </c>
+      <c r="C26">
+        <v>9</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26">
+        <v>3</v>
+      </c>
+      <c r="F26">
+        <v>7</v>
+      </c>
+      <c r="G26">
+        <v>16</v>
+      </c>
+      <c r="H26">
+        <v>16</v>
+      </c>
+      <c r="I26">
+        <f>(H26/$H$65)*100</f>
+        <v>106.66666666666667</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27">
+        <v>9</v>
+      </c>
+      <c r="C27">
+        <v>9</v>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+      <c r="E27">
+        <v>3</v>
+      </c>
+      <c r="F27">
+        <v>7</v>
+      </c>
+      <c r="G27">
+        <v>13</v>
+      </c>
+      <c r="H27">
+        <v>13</v>
+      </c>
+      <c r="I27">
+        <f>(H27/$H$65)*100</f>
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28">
+        <v>8</v>
+      </c>
+      <c r="C28">
+        <v>8</v>
+      </c>
+      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28">
+        <v>3</v>
+      </c>
+      <c r="F28">
+        <v>7</v>
+      </c>
+      <c r="G28">
+        <v>15</v>
+      </c>
+      <c r="H28">
+        <v>15</v>
+      </c>
+      <c r="I28">
+        <f>(H28/$H$65)*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29">
+        <v>10</v>
+      </c>
+      <c r="C29">
+        <v>6</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>3</v>
+      </c>
+      <c r="F29">
+        <v>7</v>
+      </c>
+      <c r="G29">
+        <v>15</v>
+      </c>
+      <c r="H29">
+        <v>15</v>
+      </c>
+      <c r="I29">
+        <f>(H29/$H$65)*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30">
+        <v>9</v>
+      </c>
+      <c r="C30">
+        <v>8</v>
+      </c>
+      <c r="D30">
+        <v>7</v>
+      </c>
+      <c r="E30">
+        <v>4</v>
+      </c>
+      <c r="F30">
+        <v>7</v>
+      </c>
+      <c r="G30">
+        <v>17</v>
+      </c>
+      <c r="H30">
+        <v>17</v>
+      </c>
+      <c r="I30">
+        <f>(H30/$H$65)*100</f>
+        <v>113.33333333333333</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31">
+        <v>10</v>
+      </c>
+      <c r="C31">
+        <v>7</v>
+      </c>
+      <c r="D31">
+        <v>5</v>
+      </c>
+      <c r="E31">
+        <v>4</v>
+      </c>
+      <c r="F31">
+        <v>7</v>
+      </c>
+      <c r="G31">
+        <v>11</v>
+      </c>
+      <c r="H31">
+        <v>11</v>
+      </c>
+      <c r="I31">
+        <f>(H31/$H$65)*100</f>
+        <v>73.333333333333329</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32">
+        <v>10</v>
+      </c>
+      <c r="C32">
+        <v>5</v>
+      </c>
+      <c r="D32">
+        <v>3</v>
+      </c>
+      <c r="E32">
+        <v>2</v>
+      </c>
+      <c r="F32">
+        <v>7</v>
+      </c>
+      <c r="G32">
+        <v>15</v>
+      </c>
+      <c r="H32">
+        <v>15</v>
+      </c>
+      <c r="I32">
+        <f>(H32/$H$65)*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33">
+        <v>9</v>
+      </c>
+      <c r="C33">
+        <v>8</v>
+      </c>
+      <c r="D33">
+        <v>5</v>
+      </c>
+      <c r="E33">
+        <v>4</v>
+      </c>
+      <c r="F33">
+        <v>7</v>
+      </c>
+      <c r="G33">
+        <v>16</v>
+      </c>
+      <c r="H33">
+        <v>16</v>
+      </c>
+      <c r="I33">
+        <f>(H33/$H$65)*100</f>
+        <v>106.66666666666667</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34">
+        <v>9</v>
+      </c>
+      <c r="C34">
+        <v>7</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="E34">
+        <v>4</v>
+      </c>
+      <c r="F34">
+        <v>7</v>
+      </c>
+      <c r="G34">
+        <v>14</v>
+      </c>
+      <c r="H34">
+        <v>14</v>
+      </c>
+      <c r="I34">
+        <f>(H34/$H$65)*100</f>
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35">
+        <v>9</v>
+      </c>
+      <c r="C35">
+        <v>9</v>
+      </c>
+      <c r="D35">
+        <v>8</v>
+      </c>
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="F35">
+        <v>7</v>
+      </c>
+      <c r="G35">
+        <v>14</v>
+      </c>
+      <c r="H35">
+        <v>14</v>
+      </c>
+      <c r="I35">
+        <f>(H35/$H$65)*100</f>
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36">
+        <v>9</v>
+      </c>
+      <c r="C36">
+        <v>8</v>
+      </c>
+      <c r="D36">
+        <v>6</v>
+      </c>
+      <c r="E36">
+        <v>3</v>
+      </c>
+      <c r="F36">
+        <v>7</v>
+      </c>
+      <c r="G36">
+        <v>14</v>
+      </c>
+      <c r="H36">
+        <v>14</v>
+      </c>
+      <c r="I36">
+        <f>(H36/$H$65)*100</f>
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37">
+        <v>10</v>
+      </c>
+      <c r="C37">
+        <v>9</v>
+      </c>
+      <c r="D37">
+        <v>7</v>
+      </c>
+      <c r="E37">
+        <v>4</v>
+      </c>
+      <c r="F37">
+        <v>7</v>
+      </c>
+      <c r="G37">
+        <v>16</v>
+      </c>
+      <c r="H37">
+        <v>16</v>
+      </c>
+      <c r="I37">
+        <f>(H37/$H$65)*100</f>
+        <v>106.66666666666667</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38">
+        <v>9</v>
+      </c>
+      <c r="C38">
+        <v>7</v>
+      </c>
+      <c r="D38">
+        <v>8</v>
+      </c>
+      <c r="E38">
+        <v>4</v>
+      </c>
+      <c r="F38">
+        <v>7</v>
+      </c>
+      <c r="G38">
+        <v>16</v>
+      </c>
+      <c r="H38">
+        <v>16</v>
+      </c>
+      <c r="I38">
+        <f>(H38/$H$65)*100</f>
+        <v>106.66666666666667</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39">
+        <v>10</v>
+      </c>
+      <c r="C39">
+        <v>7</v>
+      </c>
+      <c r="D39">
+        <v>4</v>
+      </c>
+      <c r="E39">
+        <v>2</v>
+      </c>
+      <c r="F39">
+        <v>7</v>
+      </c>
+      <c r="G39">
+        <v>13</v>
+      </c>
+      <c r="H39">
+        <v>13</v>
+      </c>
+      <c r="I39">
+        <f>(H39/$H$65)*100</f>
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40">
+        <v>9</v>
+      </c>
+      <c r="C40">
+        <v>7</v>
+      </c>
+      <c r="D40">
+        <v>7</v>
+      </c>
+      <c r="E40">
+        <v>3</v>
+      </c>
+      <c r="F40">
+        <v>7</v>
+      </c>
+      <c r="G40">
+        <v>14</v>
+      </c>
+      <c r="H40">
+        <v>14</v>
+      </c>
+      <c r="I40">
+        <f>(H40/$H$65)*100</f>
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41">
+        <v>8</v>
+      </c>
+      <c r="C41">
+        <v>9</v>
+      </c>
+      <c r="D41">
+        <v>6</v>
+      </c>
+      <c r="E41">
+        <v>4</v>
+      </c>
+      <c r="F41">
+        <v>7</v>
+      </c>
+      <c r="G41">
+        <v>15</v>
+      </c>
+      <c r="H41">
+        <v>15</v>
+      </c>
+      <c r="I41">
+        <f>(H41/$H$65)*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42">
+        <v>9</v>
+      </c>
+      <c r="C42">
+        <v>9</v>
+      </c>
+      <c r="D42">
+        <v>4</v>
+      </c>
+      <c r="E42">
+        <v>4</v>
+      </c>
+      <c r="F42">
+        <v>7</v>
+      </c>
+      <c r="G42">
+        <v>14</v>
+      </c>
+      <c r="H42">
+        <v>14</v>
+      </c>
+      <c r="I42">
+        <f>(H42/$H$65)*100</f>
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43">
+        <v>9</v>
+      </c>
+      <c r="C43">
+        <v>8</v>
+      </c>
+      <c r="D43">
+        <v>5</v>
+      </c>
+      <c r="E43">
+        <v>3</v>
+      </c>
+      <c r="F43">
+        <v>7</v>
+      </c>
+      <c r="G43">
+        <v>16</v>
+      </c>
+      <c r="H43">
+        <v>16</v>
+      </c>
+      <c r="I43">
+        <f>(H43/$H$65)*100</f>
+        <v>106.66666666666667</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44">
+        <v>8</v>
+      </c>
+      <c r="C44">
+        <v>6</v>
+      </c>
+      <c r="D44">
+        <v>4</v>
+      </c>
+      <c r="E44">
+        <v>3</v>
+      </c>
+      <c r="F44">
+        <v>7</v>
+      </c>
+      <c r="G44">
+        <v>13</v>
+      </c>
+      <c r="H44">
+        <v>13</v>
+      </c>
+      <c r="I44">
+        <f>(H44/$H$65)*100</f>
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45">
+        <v>10</v>
+      </c>
+      <c r="C45">
+        <v>10</v>
+      </c>
+      <c r="D45">
+        <v>5</v>
+      </c>
+      <c r="E45">
+        <v>3</v>
+      </c>
+      <c r="F45">
+        <v>7</v>
+      </c>
+      <c r="G45">
+        <v>16</v>
+      </c>
+      <c r="H45">
+        <v>16</v>
+      </c>
+      <c r="I45">
+        <f>(H45/$H$65)*100</f>
+        <v>106.66666666666667</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46">
+        <v>8</v>
+      </c>
+      <c r="C46">
+        <v>9</v>
+      </c>
+      <c r="D46">
+        <v>6</v>
+      </c>
+      <c r="E46">
+        <v>3</v>
+      </c>
+      <c r="F46">
+        <v>7</v>
+      </c>
+      <c r="G46">
+        <v>14</v>
+      </c>
+      <c r="H46">
+        <v>14</v>
+      </c>
+      <c r="I46">
+        <f>(H46/$H$65)*100</f>
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47">
+        <v>7</v>
+      </c>
+      <c r="C47">
+        <v>10</v>
+      </c>
+      <c r="D47">
+        <v>6</v>
+      </c>
+      <c r="E47">
+        <v>4</v>
+      </c>
+      <c r="F47">
+        <v>7</v>
+      </c>
+      <c r="G47">
+        <v>15</v>
+      </c>
+      <c r="H47">
+        <v>15</v>
+      </c>
+      <c r="I47">
+        <f>(H47/$H$65)*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48">
+        <v>9</v>
+      </c>
+      <c r="C48">
+        <v>9</v>
+      </c>
+      <c r="D48">
+        <v>6</v>
+      </c>
+      <c r="E48">
+        <v>3</v>
+      </c>
+      <c r="F48">
+        <v>7</v>
+      </c>
+      <c r="G48">
+        <v>16</v>
+      </c>
+      <c r="H48">
+        <v>16</v>
+      </c>
+      <c r="I48">
+        <f>(H48/$H$65)*100</f>
+        <v>106.66666666666667</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49">
+        <v>7</v>
+      </c>
+      <c r="C49">
+        <v>9</v>
+      </c>
+      <c r="D49">
+        <v>5</v>
+      </c>
+      <c r="E49">
+        <v>4</v>
+      </c>
+      <c r="F49">
+        <v>7</v>
+      </c>
+      <c r="G49">
+        <v>13</v>
+      </c>
+      <c r="H49">
+        <v>13</v>
+      </c>
+      <c r="I49">
+        <f>(H49/$H$65)*100</f>
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50">
+        <v>10</v>
+      </c>
+      <c r="C50">
+        <v>10</v>
+      </c>
+      <c r="D50">
+        <v>7</v>
+      </c>
+      <c r="E50">
+        <v>3</v>
+      </c>
+      <c r="F50">
+        <v>7</v>
+      </c>
+      <c r="G50">
+        <v>16</v>
+      </c>
+      <c r="H50">
+        <v>16</v>
+      </c>
+      <c r="I50">
+        <f>(H50/$H$65)*100</f>
+        <v>106.66666666666667</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>54</v>
+      </c>
+      <c r="B51">
+        <v>10</v>
+      </c>
+      <c r="C51">
+        <v>8</v>
+      </c>
+      <c r="D51">
+        <v>7</v>
+      </c>
+      <c r="E51">
+        <v>4</v>
+      </c>
+      <c r="F51">
+        <v>7</v>
+      </c>
+      <c r="G51">
+        <v>13</v>
+      </c>
+      <c r="H51">
+        <v>13</v>
+      </c>
+      <c r="I51">
+        <f>(H51/$H$65)*100</f>
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>55</v>
+      </c>
+      <c r="B52">
+        <v>8</v>
+      </c>
+      <c r="C52">
+        <v>9</v>
+      </c>
+      <c r="D52">
+        <v>5</v>
+      </c>
+      <c r="E52">
+        <v>3</v>
+      </c>
+      <c r="F52">
+        <v>7</v>
+      </c>
+      <c r="G52">
+        <v>19</v>
+      </c>
+      <c r="H52">
+        <v>19</v>
+      </c>
+      <c r="I52">
+        <f>(H52/$H$65)*100</f>
+        <v>126.66666666666666</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53">
+        <v>10</v>
+      </c>
+      <c r="C53">
+        <v>9</v>
+      </c>
+      <c r="D53">
+        <v>4</v>
+      </c>
+      <c r="E53">
+        <v>3</v>
+      </c>
+      <c r="F53">
+        <v>7</v>
+      </c>
+      <c r="G53">
+        <v>14</v>
+      </c>
+      <c r="H53">
+        <v>14</v>
+      </c>
+      <c r="I53">
+        <f>(H53/$H$65)*100</f>
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>57</v>
+      </c>
+      <c r="B54">
+        <v>10</v>
+      </c>
+      <c r="C54">
+        <v>10</v>
+      </c>
+      <c r="D54">
+        <v>4</v>
+      </c>
+      <c r="E54">
+        <v>4</v>
+      </c>
+      <c r="F54">
+        <v>7</v>
+      </c>
+      <c r="G54">
+        <v>14</v>
+      </c>
+      <c r="H54">
+        <v>14</v>
+      </c>
+      <c r="I54">
+        <f>(H54/$H$65)*100</f>
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>58</v>
+      </c>
+      <c r="B55">
+        <v>10</v>
+      </c>
+      <c r="C55">
+        <v>9</v>
+      </c>
+      <c r="D55">
+        <v>7</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>7</v>
+      </c>
+      <c r="G55">
+        <v>15</v>
+      </c>
+      <c r="H55">
+        <v>15</v>
+      </c>
+      <c r="I55">
+        <f>(H55/$H$65)*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>59</v>
+      </c>
+      <c r="B56">
+        <v>9</v>
+      </c>
+      <c r="C56">
+        <v>8</v>
+      </c>
+      <c r="D56">
+        <v>2</v>
+      </c>
+      <c r="E56">
+        <v>2</v>
+      </c>
+      <c r="F56">
+        <v>7</v>
+      </c>
+      <c r="G56">
+        <v>15</v>
+      </c>
+      <c r="H56">
+        <v>15</v>
+      </c>
+      <c r="I56">
+        <f>(H56/$H$65)*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>60</v>
+      </c>
+      <c r="B57">
+        <v>9</v>
+      </c>
+      <c r="C57">
+        <v>8</v>
+      </c>
+      <c r="D57">
+        <v>5</v>
+      </c>
+      <c r="E57">
+        <v>4</v>
+      </c>
+      <c r="F57">
+        <v>7</v>
+      </c>
+      <c r="G57">
+        <v>13</v>
+      </c>
+      <c r="H57">
+        <v>13</v>
+      </c>
+      <c r="I57">
+        <f>(H57/$H$65)*100</f>
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>61</v>
+      </c>
+      <c r="B58">
+        <v>10</v>
+      </c>
+      <c r="C58">
+        <v>6</v>
+      </c>
+      <c r="D58">
+        <v>4</v>
+      </c>
+      <c r="E58">
+        <v>4</v>
+      </c>
+      <c r="F58">
+        <v>7</v>
+      </c>
+      <c r="G58">
+        <v>13</v>
+      </c>
+      <c r="H58">
+        <v>13</v>
+      </c>
+      <c r="I58">
+        <f>(H58/$H$65)*100</f>
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>62</v>
+      </c>
+      <c r="B59">
+        <v>8</v>
+      </c>
+      <c r="C59">
+        <v>9</v>
+      </c>
+      <c r="D59">
+        <v>7</v>
+      </c>
+      <c r="E59">
+        <v>2</v>
+      </c>
+      <c r="F59">
+        <v>7</v>
+      </c>
+      <c r="G59">
+        <v>13</v>
+      </c>
+      <c r="H59">
+        <v>13</v>
+      </c>
+      <c r="I59">
+        <f>(H59/$H$65)*100</f>
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>63</v>
+      </c>
+      <c r="B60">
+        <v>10</v>
+      </c>
+      <c r="C60">
+        <v>10</v>
+      </c>
+      <c r="D60">
+        <v>3</v>
+      </c>
+      <c r="E60">
+        <v>3</v>
+      </c>
+      <c r="F60">
+        <v>7</v>
+      </c>
+      <c r="G60">
+        <v>15</v>
+      </c>
+      <c r="H60">
+        <v>15</v>
+      </c>
+      <c r="I60">
+        <f>(H60/$H$65)*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>64</v>
+      </c>
+      <c r="B61">
+        <v>9</v>
+      </c>
+      <c r="C61">
+        <v>6</v>
+      </c>
+      <c r="D61">
+        <v>5</v>
+      </c>
+      <c r="E61">
+        <v>4</v>
+      </c>
+      <c r="F61">
+        <v>7</v>
+      </c>
+      <c r="G61">
+        <v>12</v>
+      </c>
+      <c r="H61">
+        <v>12</v>
+      </c>
+      <c r="I61">
+        <f>(H61/$H$65)*100</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>65</v>
+      </c>
+      <c r="B62">
+        <v>10</v>
+      </c>
+      <c r="C62">
+        <v>10</v>
+      </c>
+      <c r="D62">
+        <v>7</v>
+      </c>
+      <c r="E62">
+        <v>3</v>
+      </c>
+      <c r="F62">
+        <v>7</v>
+      </c>
+      <c r="G62">
+        <v>14</v>
+      </c>
+      <c r="H62">
+        <v>14</v>
+      </c>
+      <c r="I62">
+        <f>(H62/$H$65)*100</f>
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>56</v>
+      </c>
+      <c r="B63">
+        <v>10</v>
+      </c>
+      <c r="C63">
+        <v>9</v>
+      </c>
+      <c r="D63">
+        <v>4</v>
+      </c>
+      <c r="E63">
+        <v>3</v>
+      </c>
+      <c r="F63">
+        <v>7</v>
+      </c>
+      <c r="G63">
+        <v>14</v>
+      </c>
+      <c r="H63">
+        <v>14</v>
+      </c>
+      <c r="I63">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>57</v>
+      </c>
+      <c r="B64">
+        <v>10</v>
+      </c>
+      <c r="C64">
+        <v>10</v>
+      </c>
+      <c r="D64">
+        <v>4</v>
+      </c>
+      <c r="E64">
+        <v>4</v>
+      </c>
+      <c r="F64">
+        <v>7</v>
+      </c>
+      <c r="G64">
+        <v>14</v>
+      </c>
+      <c r="H64">
+        <v>14</v>
+      </c>
+      <c r="I64">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>58</v>
+      </c>
+      <c r="B65">
+        <v>10</v>
+      </c>
+      <c r="C65">
+        <v>9</v>
+      </c>
+      <c r="D65">
+        <v>7</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65">
+        <v>7</v>
+      </c>
+      <c r="G65">
+        <v>15</v>
+      </c>
+      <c r="H65">
+        <v>15</v>
+      </c>
+      <c r="I65">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>59</v>
+      </c>
+      <c r="B66">
+        <v>9</v>
+      </c>
+      <c r="C66">
+        <v>8</v>
+      </c>
+      <c r="D66">
+        <v>2</v>
+      </c>
+      <c r="E66">
+        <v>2</v>
+      </c>
+      <c r="F66">
+        <v>7</v>
+      </c>
+      <c r="G66">
+        <v>15</v>
+      </c>
+      <c r="H66">
+        <v>15</v>
+      </c>
+      <c r="I66">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>60</v>
+      </c>
+      <c r="B67">
+        <v>9</v>
+      </c>
+      <c r="C67">
+        <v>8</v>
+      </c>
+      <c r="D67">
+        <v>5</v>
+      </c>
+      <c r="E67">
+        <v>4</v>
+      </c>
+      <c r="F67">
+        <v>7</v>
+      </c>
+      <c r="G67">
+        <v>13</v>
+      </c>
+      <c r="H67">
+        <v>13</v>
+      </c>
+      <c r="I67">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>61</v>
+      </c>
+      <c r="B68">
+        <v>10</v>
+      </c>
+      <c r="C68">
+        <v>6</v>
+      </c>
+      <c r="D68">
+        <v>4</v>
+      </c>
+      <c r="E68">
+        <v>4</v>
+      </c>
+      <c r="F68">
+        <v>7</v>
+      </c>
+      <c r="G68">
+        <v>13</v>
+      </c>
+      <c r="H68">
+        <v>13</v>
+      </c>
+      <c r="I68">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>62</v>
+      </c>
+      <c r="B69">
+        <v>8</v>
+      </c>
+      <c r="C69">
+        <v>9</v>
+      </c>
+      <c r="D69">
+        <v>7</v>
+      </c>
+      <c r="E69">
+        <v>2</v>
+      </c>
+      <c r="F69">
+        <v>7</v>
+      </c>
+      <c r="G69">
+        <v>13</v>
+      </c>
+      <c r="H69">
+        <v>13</v>
+      </c>
+      <c r="I69">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>63</v>
+      </c>
+      <c r="B70">
+        <v>10</v>
+      </c>
+      <c r="C70">
+        <v>10</v>
+      </c>
+      <c r="D70">
+        <v>3</v>
+      </c>
+      <c r="E70">
+        <v>3</v>
+      </c>
+      <c r="F70">
+        <v>7</v>
+      </c>
+      <c r="G70">
+        <v>15</v>
+      </c>
+      <c r="H70">
+        <v>15</v>
+      </c>
+      <c r="I70">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>64</v>
+      </c>
+      <c r="B71">
+        <v>9</v>
+      </c>
+      <c r="C71">
+        <v>6</v>
+      </c>
+      <c r="D71">
+        <v>5</v>
+      </c>
+      <c r="E71">
+        <v>4</v>
+      </c>
+      <c r="F71">
+        <v>7</v>
+      </c>
+      <c r="G71">
+        <v>12</v>
+      </c>
+      <c r="H71">
+        <v>12</v>
+      </c>
+      <c r="I71">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>65</v>
+      </c>
+      <c r="B72">
+        <v>10</v>
+      </c>
+      <c r="C72">
+        <v>10</v>
+      </c>
+      <c r="D72">
+        <v>7</v>
+      </c>
+      <c r="E72">
+        <v>3</v>
+      </c>
+      <c r="F72">
+        <v>7</v>
+      </c>
+      <c r="G72">
+        <v>14</v>
+      </c>
+      <c r="H72">
+        <v>14</v>
+      </c>
+      <c r="I72">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>66</v>
+      </c>
+      <c r="B73">
+        <v>10</v>
+      </c>
+      <c r="C73">
+        <v>10</v>
+      </c>
+      <c r="D73">
+        <v>3</v>
+      </c>
+      <c r="E73">
+        <v>5</v>
+      </c>
+      <c r="F73">
+        <v>7</v>
+      </c>
+      <c r="G73">
+        <v>12</v>
+      </c>
+      <c r="H73">
+        <v>12</v>
+      </c>
+      <c r="I73">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>67</v>
+      </c>
+      <c r="B74">
+        <v>8</v>
+      </c>
+      <c r="C74">
+        <v>11</v>
+      </c>
+      <c r="D74">
+        <v>6</v>
+      </c>
+      <c r="E74">
+        <v>4</v>
+      </c>
+      <c r="F74">
+        <v>7</v>
+      </c>
+      <c r="G74">
+        <v>13</v>
+      </c>
+      <c r="H74">
+        <v>13</v>
+      </c>
+      <c r="I74">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>58</v>
+      </c>
+      <c r="B75">
+        <v>10</v>
+      </c>
+      <c r="C75">
+        <v>9</v>
+      </c>
+      <c r="D75">
+        <v>7</v>
+      </c>
+      <c r="E75">
+        <v>1</v>
+      </c>
+      <c r="F75">
+        <v>7</v>
+      </c>
+      <c r="G75">
+        <v>15</v>
+      </c>
+      <c r="H75">
+        <v>15</v>
+      </c>
+      <c r="I75">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>59</v>
+      </c>
+      <c r="B76">
+        <v>9</v>
+      </c>
+      <c r="C76">
+        <v>8</v>
+      </c>
+      <c r="D76">
+        <v>2</v>
+      </c>
+      <c r="E76">
+        <v>2</v>
+      </c>
+      <c r="F76">
+        <v>7</v>
+      </c>
+      <c r="G76">
+        <v>15</v>
+      </c>
+      <c r="H76">
+        <v>15</v>
+      </c>
+      <c r="I76">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>60</v>
+      </c>
+      <c r="B77">
+        <v>9</v>
+      </c>
+      <c r="C77">
+        <v>8</v>
+      </c>
+      <c r="D77">
+        <v>5</v>
+      </c>
+      <c r="E77">
+        <v>4</v>
+      </c>
+      <c r="F77">
+        <v>7</v>
+      </c>
+      <c r="G77">
+        <v>13</v>
+      </c>
+      <c r="H77">
+        <v>13</v>
+      </c>
+      <c r="I77">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>61</v>
+      </c>
+      <c r="B78">
+        <v>10</v>
+      </c>
+      <c r="C78">
+        <v>6</v>
+      </c>
+      <c r="D78">
+        <v>4</v>
+      </c>
+      <c r="E78">
+        <v>4</v>
+      </c>
+      <c r="F78">
+        <v>7</v>
+      </c>
+      <c r="G78">
+        <v>13</v>
+      </c>
+      <c r="H78">
+        <v>13</v>
+      </c>
+      <c r="I78">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>62</v>
+      </c>
+      <c r="B79">
+        <v>8</v>
+      </c>
+      <c r="C79">
+        <v>9</v>
+      </c>
+      <c r="D79">
+        <v>7</v>
+      </c>
+      <c r="E79">
+        <v>2</v>
+      </c>
+      <c r="F79">
+        <v>7</v>
+      </c>
+      <c r="G79">
+        <v>13</v>
+      </c>
+      <c r="H79">
+        <v>13</v>
+      </c>
+      <c r="I79">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>63</v>
+      </c>
+      <c r="B80">
+        <v>10</v>
+      </c>
+      <c r="C80">
+        <v>10</v>
+      </c>
+      <c r="D80">
+        <v>3</v>
+      </c>
+      <c r="E80">
+        <v>3</v>
+      </c>
+      <c r="F80">
+        <v>7</v>
+      </c>
+      <c r="G80">
+        <v>15</v>
+      </c>
+      <c r="H80">
+        <v>15</v>
+      </c>
+      <c r="I80">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>64</v>
+      </c>
+      <c r="B81">
+        <v>9</v>
+      </c>
+      <c r="C81">
+        <v>6</v>
+      </c>
+      <c r="D81">
+        <v>5</v>
+      </c>
+      <c r="E81">
+        <v>4</v>
+      </c>
+      <c r="F81">
+        <v>7</v>
+      </c>
+      <c r="G81">
+        <v>12</v>
+      </c>
+      <c r="H81">
+        <v>12</v>
+      </c>
+      <c r="I81">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>65</v>
+      </c>
+      <c r="B82">
+        <v>10</v>
+      </c>
+      <c r="C82">
+        <v>10</v>
+      </c>
+      <c r="D82">
+        <v>7</v>
+      </c>
+      <c r="E82">
+        <v>3</v>
+      </c>
+      <c r="F82">
+        <v>7</v>
+      </c>
+      <c r="G82">
+        <v>14</v>
+      </c>
+      <c r="H82">
+        <v>14</v>
+      </c>
+      <c r="I82">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>66</v>
+      </c>
+      <c r="B83">
+        <v>10</v>
+      </c>
+      <c r="C83">
+        <v>10</v>
+      </c>
+      <c r="D83">
+        <v>3</v>
+      </c>
+      <c r="E83">
+        <v>5</v>
+      </c>
+      <c r="F83">
+        <v>7</v>
+      </c>
+      <c r="G83">
+        <v>12</v>
+      </c>
+      <c r="H83">
+        <v>12</v>
+      </c>
+      <c r="I83">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>71</v>
+      </c>
+      <c r="B84">
+        <v>20</v>
+      </c>
+      <c r="C84">
+        <v>20</v>
+      </c>
+      <c r="D84">
+        <v>20</v>
+      </c>
+      <c r="E84">
+        <v>20</v>
+      </c>
+      <c r="F84">
+        <v>20</v>
+      </c>
+      <c r="G84">
+        <v>20</v>
+      </c>
+      <c r="H84">
+        <v>20</v>
+      </c>
+      <c r="I84">
         <v>100</v>
       </c>
     </row>

--- a/Vac Report Template.xlsx
+++ b/Vac Report Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\General\Desktop\Dev Files\Reports_Generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E631CE-673E-4EF7-9728-FC3E38FD0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C46003C-8731-4011-8AA4-34A10E93B102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>Name</t>
   </si>
@@ -237,12 +237,6 @@
     <t>Aug 2026</t>
   </si>
   <si>
-    <t>test 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total </t>
-  </si>
-  <si>
     <t>Mr Chilwa</t>
   </si>
   <si>
@@ -250,6 +244,9 @@
   </si>
   <si>
     <t>Class Teacher:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL </t>
   </si>
 </sst>
 </file>
@@ -285,7 +282,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -293,6 +290,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -573,23 +571,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="31.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -599,17 +597,17 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -619,7 +617,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -636,19 +634,13 @@
         <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" t="s">
         <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>5</v>
-      </c>
-      <c r="I6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -665,20 +657,18 @@
         <v>3</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>12</v>
-      </c>
-      <c r="I7">
-        <f>(H7/$H$65)*100</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B7:F7)</f>
+        <v>6.8</v>
+      </c>
+      <c r="H7" s="3">
+        <f>(G7/$G$65)*100</f>
+        <v>59.649122807017541</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -695,20 +685,18 @@
         <v>2</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>12</v>
-      </c>
-      <c r="H8">
-        <v>12</v>
-      </c>
-      <c r="I8">
-        <f>(H8/$H$65)*100</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B8:F8)</f>
+        <v>7.2</v>
+      </c>
+      <c r="H8" s="3">
+        <f t="shared" ref="H8:H65" si="0">(G8/$G$65)*100</f>
+        <v>63.157894736842103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -725,20 +713,18 @@
         <v>2</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>13</v>
-      </c>
-      <c r="H9">
-        <v>13</v>
-      </c>
-      <c r="I9">
-        <f>(H9/$H$65)*100</f>
-        <v>86.666666666666671</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B9:F9)</f>
+        <v>7.4</v>
+      </c>
+      <c r="H9" s="3">
+        <f t="shared" si="0"/>
+        <v>64.912280701754383</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -755,20 +741,18 @@
         <v>5</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G10">
-        <v>12</v>
-      </c>
-      <c r="H10">
-        <v>12</v>
-      </c>
-      <c r="I10">
-        <f>(H10/$H$65)*100</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B10:F10)</f>
+        <v>8.6</v>
+      </c>
+      <c r="H10" s="3">
+        <f t="shared" si="0"/>
+        <v>75.438596491228054</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -785,20 +769,18 @@
         <v>2</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G11">
-        <v>14</v>
-      </c>
-      <c r="H11">
-        <v>14</v>
-      </c>
-      <c r="I11">
-        <f>(H11/$H$65)*100</f>
-        <v>93.333333333333329</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B11:F11)</f>
+        <v>7.8</v>
+      </c>
+      <c r="H11" s="3">
+        <f t="shared" si="0"/>
+        <v>68.421052631578945</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -815,20 +797,18 @@
         <v>3</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G12">
-        <v>15</v>
-      </c>
-      <c r="H12">
-        <v>15</v>
-      </c>
-      <c r="I12">
-        <f>(H12/$H$65)*100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B12:F12)</f>
+        <v>7.8</v>
+      </c>
+      <c r="H12" s="3">
+        <f t="shared" si="0"/>
+        <v>68.421052631578945</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -845,20 +825,18 @@
         <v>2</v>
       </c>
       <c r="F13">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G13">
-        <v>15</v>
-      </c>
-      <c r="H13">
-        <v>15</v>
-      </c>
-      <c r="I13">
-        <f>(H13/$H$65)*100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B13:F13)</f>
+        <v>8</v>
+      </c>
+      <c r="H13" s="3">
+        <f t="shared" si="0"/>
+        <v>70.175438596491219</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -875,20 +853,18 @@
         <v>5</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G14">
-        <v>13</v>
-      </c>
-      <c r="H14">
-        <v>13</v>
-      </c>
-      <c r="I14">
-        <f>(H14/$H$65)*100</f>
-        <v>86.666666666666671</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B14:F14)</f>
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
+        <f t="shared" si="0"/>
+        <v>70.175438596491219</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -905,20 +881,18 @@
         <v>3</v>
       </c>
       <c r="F15">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G15">
-        <v>14</v>
-      </c>
-      <c r="H15">
-        <v>14</v>
-      </c>
-      <c r="I15">
-        <f>(H15/$H$65)*100</f>
-        <v>93.333333333333329</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B15:F15)</f>
+        <v>7.2</v>
+      </c>
+      <c r="H15" s="3">
+        <f t="shared" si="0"/>
+        <v>63.157894736842103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -935,20 +909,18 @@
         <v>3</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G16">
-        <v>14</v>
-      </c>
-      <c r="H16">
-        <v>14</v>
-      </c>
-      <c r="I16">
-        <f>(H16/$H$65)*100</f>
-        <v>93.333333333333329</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B16:F16)</f>
+        <v>7.6</v>
+      </c>
+      <c r="H16" s="3">
+        <f t="shared" si="0"/>
+        <v>66.666666666666657</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -965,20 +937,18 @@
         <v>5</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G17">
-        <v>16</v>
-      </c>
-      <c r="H17">
-        <v>16</v>
-      </c>
-      <c r="I17">
-        <f>(H17/$H$65)*100</f>
-        <v>106.66666666666667</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B17:F17)</f>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H17" s="3">
+        <f t="shared" si="0"/>
+        <v>77.192982456140356</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -995,20 +965,18 @@
         <v>2</v>
       </c>
       <c r="F18">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G18">
-        <v>12</v>
-      </c>
-      <c r="H18">
-        <v>12</v>
-      </c>
-      <c r="I18">
-        <f>(H18/$H$65)*100</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B18:F18)</f>
+        <v>7.4</v>
+      </c>
+      <c r="H18" s="3">
+        <f t="shared" si="0"/>
+        <v>64.912280701754383</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1025,20 +993,18 @@
         <v>3</v>
       </c>
       <c r="F19">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G19">
-        <v>12</v>
-      </c>
-      <c r="H19">
-        <v>12</v>
-      </c>
-      <c r="I19">
-        <f>(H19/$H$65)*100</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B19:F19)</f>
+        <v>7.4</v>
+      </c>
+      <c r="H19" s="3">
+        <f t="shared" si="0"/>
+        <v>64.912280701754383</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1055,20 +1021,18 @@
         <v>3</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G20">
-        <v>16</v>
-      </c>
-      <c r="H20">
-        <v>16</v>
-      </c>
-      <c r="I20">
-        <f>(H20/$H$65)*100</f>
-        <v>106.66666666666667</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B20:F20)</f>
+        <v>8.4</v>
+      </c>
+      <c r="H20" s="3">
+        <f t="shared" si="0"/>
+        <v>73.68421052631578</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -1085,20 +1049,18 @@
         <v>3</v>
       </c>
       <c r="F21">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G21">
-        <v>17</v>
-      </c>
-      <c r="H21">
-        <v>17</v>
-      </c>
-      <c r="I21">
-        <f>(H21/$H$65)*100</f>
-        <v>113.33333333333333</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B21:F21)</f>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="H21" s="3">
+        <f t="shared" si="0"/>
+        <v>85.964912280701753</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -1115,20 +1077,18 @@
         <v>2</v>
       </c>
       <c r="F22">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G22">
-        <v>14</v>
-      </c>
-      <c r="H22">
-        <v>14</v>
-      </c>
-      <c r="I22">
-        <f>(H22/$H$65)*100</f>
-        <v>93.333333333333329</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B22:F22)</f>
+        <v>8.4</v>
+      </c>
+      <c r="H22" s="3">
+        <f t="shared" si="0"/>
+        <v>73.68421052631578</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -1145,20 +1105,18 @@
         <v>4</v>
       </c>
       <c r="F23">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G23">
-        <v>13</v>
-      </c>
-      <c r="H23">
-        <v>13</v>
-      </c>
-      <c r="I23">
-        <f>(H23/$H$65)*100</f>
-        <v>86.666666666666671</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B23:F23)</f>
+        <v>8</v>
+      </c>
+      <c r="H23" s="3">
+        <f t="shared" si="0"/>
+        <v>70.175438596491219</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1175,20 +1133,18 @@
         <v>3</v>
       </c>
       <c r="F24">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G24">
-        <v>16</v>
-      </c>
-      <c r="H24">
-        <v>16</v>
-      </c>
-      <c r="I24">
-        <f>(H24/$H$65)*100</f>
-        <v>106.66666666666667</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B24:F24)</f>
+        <v>8.4</v>
+      </c>
+      <c r="H24" s="3">
+        <f t="shared" si="0"/>
+        <v>73.68421052631578</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -1205,20 +1161,18 @@
         <v>5</v>
       </c>
       <c r="F25">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G25">
-        <v>14</v>
-      </c>
-      <c r="H25">
-        <v>14</v>
-      </c>
-      <c r="I25">
-        <f>(H25/$H$65)*100</f>
-        <v>93.333333333333329</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B25:F25)</f>
+        <v>8.6</v>
+      </c>
+      <c r="H25" s="3">
+        <f t="shared" si="0"/>
+        <v>75.438596491228054</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1235,20 +1189,18 @@
         <v>3</v>
       </c>
       <c r="F26">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G26">
-        <v>16</v>
-      </c>
-      <c r="H26">
-        <v>16</v>
-      </c>
-      <c r="I26">
-        <f>(H26/$H$65)*100</f>
-        <v>106.66666666666667</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B26:F26)</f>
+        <v>7.8</v>
+      </c>
+      <c r="H26" s="3">
+        <f t="shared" si="0"/>
+        <v>68.421052631578945</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1265,20 +1217,18 @@
         <v>3</v>
       </c>
       <c r="F27">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G27">
-        <v>13</v>
-      </c>
-      <c r="H27">
-        <v>13</v>
-      </c>
-      <c r="I27">
-        <f>(H27/$H$65)*100</f>
-        <v>86.666666666666671</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B27:F27)</f>
+        <v>7.8</v>
+      </c>
+      <c r="H27" s="3">
+        <f t="shared" si="0"/>
+        <v>68.421052631578945</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -1295,20 +1245,18 @@
         <v>3</v>
       </c>
       <c r="F28">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G28">
-        <v>15</v>
-      </c>
-      <c r="H28">
-        <v>15</v>
-      </c>
-      <c r="I28">
-        <f>(H28/$H$65)*100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B28:F28)</f>
+        <v>7.6</v>
+      </c>
+      <c r="H28" s="3">
+        <f t="shared" si="0"/>
+        <v>66.666666666666657</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -1325,20 +1273,18 @@
         <v>3</v>
       </c>
       <c r="F29">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G29">
-        <v>15</v>
-      </c>
-      <c r="H29">
-        <v>15</v>
-      </c>
-      <c r="I29">
-        <f>(H29/$H$65)*100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B29:F29)</f>
+        <v>7.6</v>
+      </c>
+      <c r="H29" s="3">
+        <f t="shared" si="0"/>
+        <v>66.666666666666657</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1355,20 +1301,18 @@
         <v>4</v>
       </c>
       <c r="F30">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G30">
-        <v>17</v>
-      </c>
-      <c r="H30">
-        <v>17</v>
-      </c>
-      <c r="I30">
-        <f>(H30/$H$65)*100</f>
-        <v>113.33333333333333</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B30:F30)</f>
+        <v>9</v>
+      </c>
+      <c r="H30" s="3">
+        <f t="shared" si="0"/>
+        <v>78.94736842105263</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1385,20 +1329,18 @@
         <v>4</v>
       </c>
       <c r="F31">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G31">
-        <v>11</v>
-      </c>
-      <c r="H31">
-        <v>11</v>
-      </c>
-      <c r="I31">
-        <f>(H31/$H$65)*100</f>
-        <v>73.333333333333329</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B31:F31)</f>
+        <v>7.4</v>
+      </c>
+      <c r="H31" s="3">
+        <f t="shared" si="0"/>
+        <v>64.912280701754383</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1415,20 +1357,18 @@
         <v>2</v>
       </c>
       <c r="F32">
+        <v>15</v>
+      </c>
+      <c r="G32">
+        <f>AVERAGE(B32:F32)</f>
         <v>7</v>
       </c>
-      <c r="G32">
-        <v>15</v>
-      </c>
-      <c r="H32">
-        <v>15</v>
-      </c>
-      <c r="I32">
-        <f>(H32/$H$65)*100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H32" s="3">
+        <f t="shared" si="0"/>
+        <v>61.403508771929829</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1445,20 +1385,18 @@
         <v>4</v>
       </c>
       <c r="F33">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G33">
-        <v>16</v>
-      </c>
-      <c r="H33">
-        <v>16</v>
-      </c>
-      <c r="I33">
-        <f>(H33/$H$65)*100</f>
-        <v>106.66666666666667</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B33:F33)</f>
+        <v>8.4</v>
+      </c>
+      <c r="H33" s="3">
+        <f t="shared" si="0"/>
+        <v>73.68421052631578</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1475,20 +1413,18 @@
         <v>4</v>
       </c>
       <c r="F34">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G34">
-        <v>14</v>
-      </c>
-      <c r="H34">
-        <v>14</v>
-      </c>
-      <c r="I34">
-        <f>(H34/$H$65)*100</f>
-        <v>93.333333333333329</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B34:F34)</f>
+        <v>7.2</v>
+      </c>
+      <c r="H34" s="3">
+        <f t="shared" si="0"/>
+        <v>63.157894736842103</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -1505,20 +1441,18 @@
         <v>2</v>
       </c>
       <c r="F35">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G35">
-        <v>14</v>
-      </c>
-      <c r="H35">
-        <v>14</v>
-      </c>
-      <c r="I35">
-        <f>(H35/$H$65)*100</f>
-        <v>93.333333333333329</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B35:F35)</f>
+        <v>8.4</v>
+      </c>
+      <c r="H35" s="3">
+        <f t="shared" si="0"/>
+        <v>73.68421052631578</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -1535,20 +1469,18 @@
         <v>3</v>
       </c>
       <c r="F36">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G36">
-        <v>14</v>
-      </c>
-      <c r="H36">
-        <v>14</v>
-      </c>
-      <c r="I36">
-        <f>(H36/$H$65)*100</f>
-        <v>93.333333333333329</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B36:F36)</f>
+        <v>8</v>
+      </c>
+      <c r="H36" s="3">
+        <f t="shared" si="0"/>
+        <v>70.175438596491219</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -1559,26 +1491,24 @@
         <v>9</v>
       </c>
       <c r="D37">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>4</v>
       </c>
       <c r="F37">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G37">
-        <v>16</v>
-      </c>
-      <c r="H37">
-        <v>16</v>
-      </c>
-      <c r="I37">
-        <f>(H37/$H$65)*100</f>
-        <v>106.66666666666667</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B37:F37)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H37" s="3">
+        <f t="shared" si="0"/>
+        <v>42.105263157894733</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -1589,26 +1519,24 @@
         <v>7</v>
       </c>
       <c r="D38">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G38">
-        <v>16</v>
-      </c>
-      <c r="H38">
-        <v>16</v>
-      </c>
-      <c r="I38">
-        <f>(H38/$H$65)*100</f>
-        <v>106.66666666666667</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B38:F38)</f>
+        <v>3.4</v>
+      </c>
+      <c r="H38" s="3">
+        <f t="shared" si="0"/>
+        <v>29.82456140350877</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -1619,26 +1547,24 @@
         <v>7</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>13</v>
-      </c>
-      <c r="H39">
-        <v>13</v>
-      </c>
-      <c r="I39">
-        <f>(H39/$H$65)*100</f>
-        <v>86.666666666666671</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B39:F39)</f>
+        <v>3.6</v>
+      </c>
+      <c r="H39" s="3">
+        <f t="shared" si="0"/>
+        <v>31.578947368421051</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -1646,29 +1572,27 @@
         <v>9</v>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D40">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G40">
-        <v>14</v>
-      </c>
-      <c r="H40">
-        <v>14</v>
-      </c>
-      <c r="I40">
-        <f>(H40/$H$65)*100</f>
-        <v>93.333333333333329</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B40:F40)</f>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H40" s="3">
+        <f t="shared" si="0"/>
+        <v>19.298245614035089</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -1676,29 +1600,27 @@
         <v>8</v>
       </c>
       <c r="C41">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D41">
         <v>6</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>15</v>
-      </c>
-      <c r="H41">
-        <v>15</v>
-      </c>
-      <c r="I41">
-        <f>(H41/$H$65)*100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B41:F41)</f>
+        <v>3</v>
+      </c>
+      <c r="H41" s="3">
+        <f t="shared" si="0"/>
+        <v>26.315789473684209</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -1715,20 +1637,18 @@
         <v>4</v>
       </c>
       <c r="F42">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G42">
-        <v>14</v>
-      </c>
-      <c r="H42">
-        <v>14</v>
-      </c>
-      <c r="I42">
-        <f>(H42/$H$65)*100</f>
-        <v>93.333333333333329</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B42:F42)</f>
+        <v>8</v>
+      </c>
+      <c r="H42" s="3">
+        <f t="shared" si="0"/>
+        <v>70.175438596491219</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -1745,20 +1665,18 @@
         <v>3</v>
       </c>
       <c r="F43">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G43">
-        <v>16</v>
-      </c>
-      <c r="H43">
-        <v>16</v>
-      </c>
-      <c r="I43">
-        <f>(H43/$H$65)*100</f>
-        <v>106.66666666666667</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B43:F43)</f>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="H43" s="3">
+        <f t="shared" si="0"/>
+        <v>71.929824561403493</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -1775,20 +1693,18 @@
         <v>3</v>
       </c>
       <c r="F44">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G44">
-        <v>13</v>
-      </c>
-      <c r="H44">
-        <v>13</v>
-      </c>
-      <c r="I44">
-        <f>(H44/$H$65)*100</f>
-        <v>86.666666666666671</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B44:F44)</f>
+        <v>6.8</v>
+      </c>
+      <c r="H44" s="3">
+        <f t="shared" si="0"/>
+        <v>59.649122807017541</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -1805,20 +1721,18 @@
         <v>3</v>
       </c>
       <c r="F45">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G45">
-        <v>16</v>
-      </c>
-      <c r="H45">
-        <v>16</v>
-      </c>
-      <c r="I45">
-        <f>(H45/$H$65)*100</f>
-        <v>106.66666666666667</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B45:F45)</f>
+        <v>5.8</v>
+      </c>
+      <c r="H45" s="3">
+        <f t="shared" si="0"/>
+        <v>50.87719298245613</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -1835,20 +1749,18 @@
         <v>3</v>
       </c>
       <c r="F46">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G46">
-        <v>14</v>
-      </c>
-      <c r="H46">
-        <v>14</v>
-      </c>
-      <c r="I46">
-        <f>(H46/$H$65)*100</f>
-        <v>93.333333333333329</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B46:F46)</f>
+        <v>8</v>
+      </c>
+      <c r="H46" s="3">
+        <f t="shared" si="0"/>
+        <v>70.175438596491219</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -1865,20 +1777,18 @@
         <v>4</v>
       </c>
       <c r="F47">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G47">
-        <v>15</v>
-      </c>
-      <c r="H47">
-        <v>15</v>
-      </c>
-      <c r="I47">
-        <f>(H47/$H$65)*100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B47:F47)</f>
+        <v>6</v>
+      </c>
+      <c r="H47" s="3">
+        <f t="shared" si="0"/>
+        <v>52.631578947368418</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>51</v>
       </c>
@@ -1895,20 +1805,18 @@
         <v>3</v>
       </c>
       <c r="F48">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G48">
-        <v>16</v>
-      </c>
-      <c r="H48">
-        <v>16</v>
-      </c>
-      <c r="I48">
-        <f>(H48/$H$65)*100</f>
-        <v>106.66666666666667</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B48:F48)</f>
+        <v>8.6</v>
+      </c>
+      <c r="H48" s="3">
+        <f t="shared" si="0"/>
+        <v>75.438596491228054</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>52</v>
       </c>
@@ -1925,20 +1833,18 @@
         <v>4</v>
       </c>
       <c r="F49">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G49">
-        <v>13</v>
-      </c>
-      <c r="H49">
-        <v>13</v>
-      </c>
-      <c r="I49">
-        <f>(H49/$H$65)*100</f>
-        <v>86.666666666666671</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B49:F49)</f>
+        <v>7.6</v>
+      </c>
+      <c r="H49" s="3">
+        <f t="shared" si="0"/>
+        <v>66.666666666666657</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -1955,20 +1861,18 @@
         <v>3</v>
       </c>
       <c r="F50">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G50">
-        <v>16</v>
-      </c>
-      <c r="H50">
-        <v>16</v>
-      </c>
-      <c r="I50">
-        <f>(H50/$H$65)*100</f>
-        <v>106.66666666666667</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B50:F50)</f>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="H50" s="3">
+        <f t="shared" si="0"/>
+        <v>80.701754385964904</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>54</v>
       </c>
@@ -1985,20 +1889,18 @@
         <v>4</v>
       </c>
       <c r="F51">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G51">
-        <v>13</v>
-      </c>
-      <c r="H51">
-        <v>13</v>
-      </c>
-      <c r="I51">
-        <f>(H51/$H$65)*100</f>
-        <v>86.666666666666671</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B51:F51)</f>
+        <v>8.4</v>
+      </c>
+      <c r="H51" s="3">
+        <f t="shared" si="0"/>
+        <v>73.68421052631578</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -2015,20 +1917,18 @@
         <v>3</v>
       </c>
       <c r="F52">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G52">
-        <v>19</v>
-      </c>
-      <c r="H52">
-        <v>19</v>
-      </c>
-      <c r="I52">
-        <f>(H52/$H$65)*100</f>
-        <v>126.66666666666666</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B52:F52)</f>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H52" s="3">
+        <f t="shared" si="0"/>
+        <v>77.192982456140356</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>56</v>
       </c>
@@ -2045,20 +1945,18 @@
         <v>3</v>
       </c>
       <c r="F53">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G53">
-        <v>14</v>
-      </c>
-      <c r="H53">
-        <v>14</v>
-      </c>
-      <c r="I53">
-        <f>(H53/$H$65)*100</f>
-        <v>93.333333333333329</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B53:F53)</f>
+        <v>8</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" si="0"/>
+        <v>70.175438596491219</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>57</v>
       </c>
@@ -2075,20 +1973,18 @@
         <v>4</v>
       </c>
       <c r="F54">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G54">
-        <v>14</v>
-      </c>
-      <c r="H54">
-        <v>14</v>
-      </c>
-      <c r="I54">
-        <f>(H54/$H$65)*100</f>
-        <v>93.333333333333329</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B54:F54)</f>
+        <v>8.4</v>
+      </c>
+      <c r="H54" s="3">
+        <f t="shared" si="0"/>
+        <v>73.68421052631578</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>58</v>
       </c>
@@ -2105,20 +2001,18 @@
         <v>1</v>
       </c>
       <c r="F55">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G55">
-        <v>15</v>
-      </c>
-      <c r="H55">
-        <v>15</v>
-      </c>
-      <c r="I55">
-        <f>(H55/$H$65)*100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B55:F55)</f>
+        <v>8.4</v>
+      </c>
+      <c r="H55" s="3">
+        <f t="shared" si="0"/>
+        <v>73.68421052631578</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>59</v>
       </c>
@@ -2135,20 +2029,18 @@
         <v>2</v>
       </c>
       <c r="F56">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G56">
-        <v>15</v>
-      </c>
-      <c r="H56">
-        <v>15</v>
-      </c>
-      <c r="I56">
-        <f>(H56/$H$65)*100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B56:F56)</f>
+        <v>7.2</v>
+      </c>
+      <c r="H56" s="3">
+        <f t="shared" si="0"/>
+        <v>63.157894736842103</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>60</v>
       </c>
@@ -2165,20 +2057,18 @@
         <v>4</v>
       </c>
       <c r="F57">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G57">
-        <v>13</v>
-      </c>
-      <c r="H57">
-        <v>13</v>
-      </c>
-      <c r="I57">
-        <f>(H57/$H$65)*100</f>
-        <v>86.666666666666671</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B57:F57)</f>
+        <v>7.8</v>
+      </c>
+      <c r="H57" s="3">
+        <f t="shared" si="0"/>
+        <v>68.421052631578945</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>61</v>
       </c>
@@ -2195,20 +2085,18 @@
         <v>4</v>
       </c>
       <c r="F58">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G58">
-        <v>13</v>
-      </c>
-      <c r="H58">
-        <v>13</v>
-      </c>
-      <c r="I58">
-        <f>(H58/$H$65)*100</f>
-        <v>86.666666666666671</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B58:F58)</f>
+        <v>7.4</v>
+      </c>
+      <c r="H58" s="3">
+        <f t="shared" si="0"/>
+        <v>64.912280701754383</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>62</v>
       </c>
@@ -2225,20 +2113,18 @@
         <v>2</v>
       </c>
       <c r="F59">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G59">
-        <v>13</v>
-      </c>
-      <c r="H59">
-        <v>13</v>
-      </c>
-      <c r="I59">
-        <f>(H59/$H$65)*100</f>
-        <v>86.666666666666671</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B59:F59)</f>
+        <v>7.8</v>
+      </c>
+      <c r="H59" s="3">
+        <f t="shared" si="0"/>
+        <v>68.421052631578945</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>63</v>
       </c>
@@ -2255,20 +2141,18 @@
         <v>3</v>
       </c>
       <c r="F60">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G60">
-        <v>15</v>
-      </c>
-      <c r="H60">
-        <v>15</v>
-      </c>
-      <c r="I60">
-        <f>(H60/$H$65)*100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B60:F60)</f>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="H60" s="3">
+        <f t="shared" si="0"/>
+        <v>71.929824561403493</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>64</v>
       </c>
@@ -2279,31 +2163,29 @@
         <v>6</v>
       </c>
       <c r="D61">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F61">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="G61">
-        <v>12</v>
-      </c>
-      <c r="H61">
-        <v>12</v>
-      </c>
-      <c r="I61">
-        <f>(H61/$H$65)*100</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B61:F61)</f>
+        <v>9.6</v>
+      </c>
+      <c r="H61" s="3">
+        <f t="shared" si="0"/>
+        <v>84.210526315789465</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>65</v>
       </c>
       <c r="B62">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C62">
         <v>10</v>
@@ -2312,660 +2194,105 @@
         <v>7</v>
       </c>
       <c r="E62">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F62">
+        <v>20</v>
+      </c>
+      <c r="G62">
+        <f>AVERAGE(B62:F62)</f>
+        <v>10.4</v>
+      </c>
+      <c r="H62" s="3">
+        <f t="shared" si="0"/>
+        <v>91.228070175438589</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>66</v>
+      </c>
+      <c r="B63">
+        <v>9</v>
+      </c>
+      <c r="C63">
+        <v>10</v>
+      </c>
+      <c r="D63">
         <v>7</v>
       </c>
-      <c r="G62">
-        <v>14</v>
-      </c>
-      <c r="H62">
-        <v>14</v>
-      </c>
-      <c r="I62">
-        <f>(H62/$H$65)*100</f>
-        <v>93.333333333333329</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>56</v>
-      </c>
-      <c r="B63">
-        <v>10</v>
-      </c>
-      <c r="C63">
-        <v>9</v>
-      </c>
-      <c r="D63">
-        <v>4</v>
-      </c>
       <c r="E63">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F63">
+        <v>19</v>
+      </c>
+      <c r="G63">
+        <f>AVERAGE(B63:F63)</f>
+        <v>10.199999999999999</v>
+      </c>
+      <c r="H63" s="3">
+        <f t="shared" si="0"/>
+        <v>89.473684210526301</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>67</v>
+      </c>
+      <c r="B64">
+        <v>9</v>
+      </c>
+      <c r="C64">
+        <v>11</v>
+      </c>
+      <c r="D64">
         <v>7</v>
       </c>
-      <c r="G63">
-        <v>14</v>
-      </c>
-      <c r="H63">
-        <v>14</v>
-      </c>
-      <c r="I63">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>57</v>
-      </c>
-      <c r="B64">
-        <v>10</v>
-      </c>
-      <c r="C64">
-        <v>10</v>
-      </c>
-      <c r="D64">
-        <v>4</v>
-      </c>
       <c r="E64">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G64">
-        <v>14</v>
-      </c>
-      <c r="H64">
-        <v>14</v>
-      </c>
-      <c r="I64">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+        <f>AVERAGE(B64:F64)</f>
+        <v>10.4</v>
+      </c>
+      <c r="H64" s="3">
+        <f t="shared" si="0"/>
+        <v>91.228070175438589</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="B65">
         <v>10</v>
       </c>
       <c r="C65">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D65">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F65">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="G65">
-        <v>15</v>
-      </c>
-      <c r="H65">
-        <v>15</v>
-      </c>
-      <c r="I65">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>59</v>
-      </c>
-      <c r="B66">
-        <v>9</v>
-      </c>
-      <c r="C66">
-        <v>8</v>
-      </c>
-      <c r="D66">
-        <v>2</v>
-      </c>
-      <c r="E66">
-        <v>2</v>
-      </c>
-      <c r="F66">
-        <v>7</v>
-      </c>
-      <c r="G66">
-        <v>15</v>
-      </c>
-      <c r="H66">
-        <v>15</v>
-      </c>
-      <c r="I66">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>60</v>
-      </c>
-      <c r="B67">
-        <v>9</v>
-      </c>
-      <c r="C67">
-        <v>8</v>
-      </c>
-      <c r="D67">
-        <v>5</v>
-      </c>
-      <c r="E67">
-        <v>4</v>
-      </c>
-      <c r="F67">
-        <v>7</v>
-      </c>
-      <c r="G67">
-        <v>13</v>
-      </c>
-      <c r="H67">
-        <v>13</v>
-      </c>
-      <c r="I67">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>61</v>
-      </c>
-      <c r="B68">
-        <v>10</v>
-      </c>
-      <c r="C68">
-        <v>6</v>
-      </c>
-      <c r="D68">
-        <v>4</v>
-      </c>
-      <c r="E68">
-        <v>4</v>
-      </c>
-      <c r="F68">
-        <v>7</v>
-      </c>
-      <c r="G68">
-        <v>13</v>
-      </c>
-      <c r="H68">
-        <v>13</v>
-      </c>
-      <c r="I68">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>62</v>
-      </c>
-      <c r="B69">
-        <v>8</v>
-      </c>
-      <c r="C69">
-        <v>9</v>
-      </c>
-      <c r="D69">
-        <v>7</v>
-      </c>
-      <c r="E69">
-        <v>2</v>
-      </c>
-      <c r="F69">
-        <v>7</v>
-      </c>
-      <c r="G69">
-        <v>13</v>
-      </c>
-      <c r="H69">
-        <v>13</v>
-      </c>
-      <c r="I69">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>63</v>
-      </c>
-      <c r="B70">
-        <v>10</v>
-      </c>
-      <c r="C70">
-        <v>10</v>
-      </c>
-      <c r="D70">
-        <v>3</v>
-      </c>
-      <c r="E70">
-        <v>3</v>
-      </c>
-      <c r="F70">
-        <v>7</v>
-      </c>
-      <c r="G70">
-        <v>15</v>
-      </c>
-      <c r="H70">
-        <v>15</v>
-      </c>
-      <c r="I70">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>64</v>
-      </c>
-      <c r="B71">
-        <v>9</v>
-      </c>
-      <c r="C71">
-        <v>6</v>
-      </c>
-      <c r="D71">
-        <v>5</v>
-      </c>
-      <c r="E71">
-        <v>4</v>
-      </c>
-      <c r="F71">
-        <v>7</v>
-      </c>
-      <c r="G71">
-        <v>12</v>
-      </c>
-      <c r="H71">
-        <v>12</v>
-      </c>
-      <c r="I71">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>65</v>
-      </c>
-      <c r="B72">
-        <v>10</v>
-      </c>
-      <c r="C72">
-        <v>10</v>
-      </c>
-      <c r="D72">
-        <v>7</v>
-      </c>
-      <c r="E72">
-        <v>3</v>
-      </c>
-      <c r="F72">
-        <v>7</v>
-      </c>
-      <c r="G72">
-        <v>14</v>
-      </c>
-      <c r="H72">
-        <v>14</v>
-      </c>
-      <c r="I72">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>66</v>
-      </c>
-      <c r="B73">
-        <v>10</v>
-      </c>
-      <c r="C73">
-        <v>10</v>
-      </c>
-      <c r="D73">
-        <v>3</v>
-      </c>
-      <c r="E73">
-        <v>5</v>
-      </c>
-      <c r="F73">
-        <v>7</v>
-      </c>
-      <c r="G73">
-        <v>12</v>
-      </c>
-      <c r="H73">
-        <v>12</v>
-      </c>
-      <c r="I73">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>67</v>
-      </c>
-      <c r="B74">
-        <v>8</v>
-      </c>
-      <c r="C74">
-        <v>11</v>
-      </c>
-      <c r="D74">
-        <v>6</v>
-      </c>
-      <c r="E74">
-        <v>4</v>
-      </c>
-      <c r="F74">
-        <v>7</v>
-      </c>
-      <c r="G74">
-        <v>13</v>
-      </c>
-      <c r="H74">
-        <v>13</v>
-      </c>
-      <c r="I74">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>58</v>
-      </c>
-      <c r="B75">
-        <v>10</v>
-      </c>
-      <c r="C75">
-        <v>9</v>
-      </c>
-      <c r="D75">
-        <v>7</v>
-      </c>
-      <c r="E75">
-        <v>1</v>
-      </c>
-      <c r="F75">
-        <v>7</v>
-      </c>
-      <c r="G75">
-        <v>15</v>
-      </c>
-      <c r="H75">
-        <v>15</v>
-      </c>
-      <c r="I75">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>59</v>
-      </c>
-      <c r="B76">
-        <v>9</v>
-      </c>
-      <c r="C76">
-        <v>8</v>
-      </c>
-      <c r="D76">
-        <v>2</v>
-      </c>
-      <c r="E76">
-        <v>2</v>
-      </c>
-      <c r="F76">
-        <v>7</v>
-      </c>
-      <c r="G76">
-        <v>15</v>
-      </c>
-      <c r="H76">
-        <v>15</v>
-      </c>
-      <c r="I76">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>60</v>
-      </c>
-      <c r="B77">
-        <v>9</v>
-      </c>
-      <c r="C77">
-        <v>8</v>
-      </c>
-      <c r="D77">
-        <v>5</v>
-      </c>
-      <c r="E77">
-        <v>4</v>
-      </c>
-      <c r="F77">
-        <v>7</v>
-      </c>
-      <c r="G77">
-        <v>13</v>
-      </c>
-      <c r="H77">
-        <v>13</v>
-      </c>
-      <c r="I77">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>61</v>
-      </c>
-      <c r="B78">
-        <v>10</v>
-      </c>
-      <c r="C78">
-        <v>6</v>
-      </c>
-      <c r="D78">
-        <v>4</v>
-      </c>
-      <c r="E78">
-        <v>4</v>
-      </c>
-      <c r="F78">
-        <v>7</v>
-      </c>
-      <c r="G78">
-        <v>13</v>
-      </c>
-      <c r="H78">
-        <v>13</v>
-      </c>
-      <c r="I78">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>62</v>
-      </c>
-      <c r="B79">
-        <v>8</v>
-      </c>
-      <c r="C79">
-        <v>9</v>
-      </c>
-      <c r="D79">
-        <v>7</v>
-      </c>
-      <c r="E79">
-        <v>2</v>
-      </c>
-      <c r="F79">
-        <v>7</v>
-      </c>
-      <c r="G79">
-        <v>13</v>
-      </c>
-      <c r="H79">
-        <v>13</v>
-      </c>
-      <c r="I79">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>63</v>
-      </c>
-      <c r="B80">
-        <v>10</v>
-      </c>
-      <c r="C80">
-        <v>10</v>
-      </c>
-      <c r="D80">
-        <v>3</v>
-      </c>
-      <c r="E80">
-        <v>3</v>
-      </c>
-      <c r="F80">
-        <v>7</v>
-      </c>
-      <c r="G80">
-        <v>15</v>
-      </c>
-      <c r="H80">
-        <v>15</v>
-      </c>
-      <c r="I80">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>64</v>
-      </c>
-      <c r="B81">
-        <v>9</v>
-      </c>
-      <c r="C81">
-        <v>6</v>
-      </c>
-      <c r="D81">
-        <v>5</v>
-      </c>
-      <c r="E81">
-        <v>4</v>
-      </c>
-      <c r="F81">
-        <v>7</v>
-      </c>
-      <c r="G81">
-        <v>12</v>
-      </c>
-      <c r="H81">
-        <v>12</v>
-      </c>
-      <c r="I81">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
-        <v>65</v>
-      </c>
-      <c r="B82">
-        <v>10</v>
-      </c>
-      <c r="C82">
-        <v>10</v>
-      </c>
-      <c r="D82">
-        <v>7</v>
-      </c>
-      <c r="E82">
-        <v>3</v>
-      </c>
-      <c r="F82">
-        <v>7</v>
-      </c>
-      <c r="G82">
-        <v>14</v>
-      </c>
-      <c r="H82">
-        <v>14</v>
-      </c>
-      <c r="I82">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
-        <v>66</v>
-      </c>
-      <c r="B83">
-        <v>10</v>
-      </c>
-      <c r="C83">
-        <v>10</v>
-      </c>
-      <c r="D83">
-        <v>3</v>
-      </c>
-      <c r="E83">
-        <v>5</v>
-      </c>
-      <c r="F83">
-        <v>7</v>
-      </c>
-      <c r="G83">
-        <v>12</v>
-      </c>
-      <c r="H83">
-        <v>12</v>
-      </c>
-      <c r="I83">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>71</v>
-      </c>
-      <c r="B84">
-        <v>20</v>
-      </c>
-      <c r="C84">
-        <v>20</v>
-      </c>
-      <c r="D84">
-        <v>20</v>
-      </c>
-      <c r="E84">
-        <v>20</v>
-      </c>
-      <c r="F84">
-        <v>20</v>
-      </c>
-      <c r="G84">
-        <v>20</v>
-      </c>
-      <c r="H84">
-        <v>20</v>
-      </c>
-      <c r="I84">
+        <f>AVERAGE(B65:F65)</f>
+        <v>11.4</v>
+      </c>
+      <c r="H65" s="3">
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
     </row>
+    <row r="66" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B1:D1"/>

--- a/Vac Report Template.xlsx
+++ b/Vac Report Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\General\Desktop\Dev Files\Reports_Generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C46003C-8731-4011-8AA4-34A10E93B102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A300E1D-D820-4BDF-94A1-2535B862182E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -237,16 +237,16 @@
     <t>Aug 2026</t>
   </si>
   <si>
-    <t>Mr Chilwa</t>
-  </si>
-  <si>
-    <t>Mathematics</t>
-  </si>
-  <si>
     <t>Class Teacher:</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL </t>
+  </si>
+  <si>
+    <t>Mr Mugoni</t>
+  </si>
+  <si>
+    <t>Biology</t>
   </si>
 </sst>
 </file>
@@ -284,13 +284,13 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -579,43 +579,43 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="B3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
@@ -660,10 +660,10 @@
         <v>12</v>
       </c>
       <c r="G7">
-        <f>AVERAGE(B7:F7)</f>
+        <f t="shared" ref="G7:G38" si="0">AVERAGE(B7:F7)</f>
         <v>6.8</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="1">
         <f>(G7/$G$65)*100</f>
         <v>59.649122807017541</v>
       </c>
@@ -688,11 +688,11 @@
         <v>12</v>
       </c>
       <c r="G8">
-        <f>AVERAGE(B8:F8)</f>
+        <f t="shared" si="0"/>
         <v>7.2</v>
       </c>
-      <c r="H8" s="3">
-        <f t="shared" ref="H8:H65" si="0">(G8/$G$65)*100</f>
+      <c r="H8" s="1">
+        <f t="shared" ref="H8:H65" si="1">(G8/$G$65)*100</f>
         <v>63.157894736842103</v>
       </c>
     </row>
@@ -716,11 +716,11 @@
         <v>13</v>
       </c>
       <c r="G9">
-        <f>AVERAGE(B9:F9)</f>
+        <f t="shared" si="0"/>
         <v>7.4</v>
       </c>
-      <c r="H9" s="3">
-        <f t="shared" si="0"/>
+      <c r="H9" s="1">
+        <f t="shared" si="1"/>
         <v>64.912280701754383</v>
       </c>
     </row>
@@ -744,11 +744,11 @@
         <v>12</v>
       </c>
       <c r="G10">
-        <f>AVERAGE(B10:F10)</f>
+        <f t="shared" si="0"/>
         <v>8.6</v>
       </c>
-      <c r="H10" s="3">
-        <f t="shared" si="0"/>
+      <c r="H10" s="1">
+        <f t="shared" si="1"/>
         <v>75.438596491228054</v>
       </c>
     </row>
@@ -772,11 +772,11 @@
         <v>14</v>
       </c>
       <c r="G11">
-        <f>AVERAGE(B11:F11)</f>
+        <f t="shared" si="0"/>
         <v>7.8</v>
       </c>
-      <c r="H11" s="3">
-        <f t="shared" si="0"/>
+      <c r="H11" s="1">
+        <f t="shared" si="1"/>
         <v>68.421052631578945</v>
       </c>
     </row>
@@ -800,11 +800,11 @@
         <v>15</v>
       </c>
       <c r="G12">
-        <f>AVERAGE(B12:F12)</f>
+        <f t="shared" si="0"/>
         <v>7.8</v>
       </c>
-      <c r="H12" s="3">
-        <f t="shared" si="0"/>
+      <c r="H12" s="1">
+        <f t="shared" si="1"/>
         <v>68.421052631578945</v>
       </c>
     </row>
@@ -828,11 +828,11 @@
         <v>15</v>
       </c>
       <c r="G13">
-        <f>AVERAGE(B13:F13)</f>
-        <v>8</v>
-      </c>
-      <c r="H13" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="H13" s="1">
+        <f t="shared" si="1"/>
         <v>70.175438596491219</v>
       </c>
     </row>
@@ -856,11 +856,11 @@
         <v>13</v>
       </c>
       <c r="G14">
-        <f>AVERAGE(B14:F14)</f>
-        <v>8</v>
-      </c>
-      <c r="H14" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="1"/>
         <v>70.175438596491219</v>
       </c>
     </row>
@@ -884,11 +884,11 @@
         <v>14</v>
       </c>
       <c r="G15">
-        <f>AVERAGE(B15:F15)</f>
+        <f t="shared" si="0"/>
         <v>7.2</v>
       </c>
-      <c r="H15" s="3">
-        <f t="shared" si="0"/>
+      <c r="H15" s="1">
+        <f t="shared" si="1"/>
         <v>63.157894736842103</v>
       </c>
     </row>
@@ -912,11 +912,11 @@
         <v>14</v>
       </c>
       <c r="G16">
-        <f>AVERAGE(B16:F16)</f>
+        <f t="shared" si="0"/>
         <v>7.6</v>
       </c>
-      <c r="H16" s="3">
-        <f t="shared" si="0"/>
+      <c r="H16" s="1">
+        <f t="shared" si="1"/>
         <v>66.666666666666657</v>
       </c>
     </row>
@@ -940,11 +940,11 @@
         <v>16</v>
       </c>
       <c r="G17">
-        <f>AVERAGE(B17:F17)</f>
+        <f t="shared" si="0"/>
         <v>8.8000000000000007</v>
       </c>
-      <c r="H17" s="3">
-        <f t="shared" si="0"/>
+      <c r="H17" s="1">
+        <f t="shared" si="1"/>
         <v>77.192982456140356</v>
       </c>
     </row>
@@ -968,11 +968,11 @@
         <v>12</v>
       </c>
       <c r="G18">
-        <f>AVERAGE(B18:F18)</f>
+        <f t="shared" si="0"/>
         <v>7.4</v>
       </c>
-      <c r="H18" s="3">
-        <f t="shared" si="0"/>
+      <c r="H18" s="1">
+        <f t="shared" si="1"/>
         <v>64.912280701754383</v>
       </c>
     </row>
@@ -996,11 +996,11 @@
         <v>12</v>
       </c>
       <c r="G19">
-        <f>AVERAGE(B19:F19)</f>
+        <f t="shared" si="0"/>
         <v>7.4</v>
       </c>
-      <c r="H19" s="3">
-        <f t="shared" si="0"/>
+      <c r="H19" s="1">
+        <f t="shared" si="1"/>
         <v>64.912280701754383</v>
       </c>
     </row>
@@ -1024,11 +1024,11 @@
         <v>16</v>
       </c>
       <c r="G20">
-        <f>AVERAGE(B20:F20)</f>
+        <f t="shared" si="0"/>
         <v>8.4</v>
       </c>
-      <c r="H20" s="3">
-        <f t="shared" si="0"/>
+      <c r="H20" s="1">
+        <f t="shared" si="1"/>
         <v>73.68421052631578</v>
       </c>
     </row>
@@ -1052,11 +1052,11 @@
         <v>17</v>
       </c>
       <c r="G21">
-        <f>AVERAGE(B21:F21)</f>
+        <f t="shared" si="0"/>
         <v>9.8000000000000007</v>
       </c>
-      <c r="H21" s="3">
-        <f t="shared" si="0"/>
+      <c r="H21" s="1">
+        <f t="shared" si="1"/>
         <v>85.964912280701753</v>
       </c>
     </row>
@@ -1080,11 +1080,11 @@
         <v>14</v>
       </c>
       <c r="G22">
-        <f>AVERAGE(B22:F22)</f>
+        <f t="shared" si="0"/>
         <v>8.4</v>
       </c>
-      <c r="H22" s="3">
-        <f t="shared" si="0"/>
+      <c r="H22" s="1">
+        <f t="shared" si="1"/>
         <v>73.68421052631578</v>
       </c>
     </row>
@@ -1108,11 +1108,11 @@
         <v>13</v>
       </c>
       <c r="G23">
-        <f>AVERAGE(B23:F23)</f>
-        <v>8</v>
-      </c>
-      <c r="H23" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="H23" s="1">
+        <f t="shared" si="1"/>
         <v>70.175438596491219</v>
       </c>
     </row>
@@ -1136,11 +1136,11 @@
         <v>16</v>
       </c>
       <c r="G24">
-        <f>AVERAGE(B24:F24)</f>
+        <f t="shared" si="0"/>
         <v>8.4</v>
       </c>
-      <c r="H24" s="3">
-        <f t="shared" si="0"/>
+      <c r="H24" s="1">
+        <f t="shared" si="1"/>
         <v>73.68421052631578</v>
       </c>
     </row>
@@ -1164,11 +1164,11 @@
         <v>14</v>
       </c>
       <c r="G25">
-        <f>AVERAGE(B25:F25)</f>
+        <f t="shared" si="0"/>
         <v>8.6</v>
       </c>
-      <c r="H25" s="3">
-        <f t="shared" si="0"/>
+      <c r="H25" s="1">
+        <f t="shared" si="1"/>
         <v>75.438596491228054</v>
       </c>
     </row>
@@ -1192,11 +1192,11 @@
         <v>16</v>
       </c>
       <c r="G26">
-        <f>AVERAGE(B26:F26)</f>
+        <f t="shared" si="0"/>
         <v>7.8</v>
       </c>
-      <c r="H26" s="3">
-        <f t="shared" si="0"/>
+      <c r="H26" s="1">
+        <f t="shared" si="1"/>
         <v>68.421052631578945</v>
       </c>
     </row>
@@ -1220,11 +1220,11 @@
         <v>13</v>
       </c>
       <c r="G27">
-        <f>AVERAGE(B27:F27)</f>
+        <f t="shared" si="0"/>
         <v>7.8</v>
       </c>
-      <c r="H27" s="3">
-        <f t="shared" si="0"/>
+      <c r="H27" s="1">
+        <f t="shared" si="1"/>
         <v>68.421052631578945</v>
       </c>
     </row>
@@ -1248,11 +1248,11 @@
         <v>15</v>
       </c>
       <c r="G28">
-        <f>AVERAGE(B28:F28)</f>
+        <f t="shared" si="0"/>
         <v>7.6</v>
       </c>
-      <c r="H28" s="3">
-        <f t="shared" si="0"/>
+      <c r="H28" s="1">
+        <f t="shared" si="1"/>
         <v>66.666666666666657</v>
       </c>
     </row>
@@ -1276,11 +1276,11 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <f>AVERAGE(B29:F29)</f>
+        <f t="shared" si="0"/>
         <v>7.6</v>
       </c>
-      <c r="H29" s="3">
-        <f t="shared" si="0"/>
+      <c r="H29" s="1">
+        <f t="shared" si="1"/>
         <v>66.666666666666657</v>
       </c>
     </row>
@@ -1304,11 +1304,11 @@
         <v>17</v>
       </c>
       <c r="G30">
-        <f>AVERAGE(B30:F30)</f>
-        <v>9</v>
-      </c>
-      <c r="H30" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="H30" s="1">
+        <f t="shared" si="1"/>
         <v>78.94736842105263</v>
       </c>
     </row>
@@ -1332,11 +1332,11 @@
         <v>11</v>
       </c>
       <c r="G31">
-        <f>AVERAGE(B31:F31)</f>
+        <f t="shared" si="0"/>
         <v>7.4</v>
       </c>
-      <c r="H31" s="3">
-        <f t="shared" si="0"/>
+      <c r="H31" s="1">
+        <f t="shared" si="1"/>
         <v>64.912280701754383</v>
       </c>
     </row>
@@ -1360,11 +1360,11 @@
         <v>15</v>
       </c>
       <c r="G32">
-        <f>AVERAGE(B32:F32)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="H32" s="3">
-        <f t="shared" si="0"/>
+      <c r="H32" s="1">
+        <f t="shared" si="1"/>
         <v>61.403508771929829</v>
       </c>
     </row>
@@ -1388,11 +1388,11 @@
         <v>16</v>
       </c>
       <c r="G33">
-        <f>AVERAGE(B33:F33)</f>
+        <f t="shared" si="0"/>
         <v>8.4</v>
       </c>
-      <c r="H33" s="3">
-        <f t="shared" si="0"/>
+      <c r="H33" s="1">
+        <f t="shared" si="1"/>
         <v>73.68421052631578</v>
       </c>
     </row>
@@ -1416,11 +1416,11 @@
         <v>14</v>
       </c>
       <c r="G34">
-        <f>AVERAGE(B34:F34)</f>
+        <f t="shared" si="0"/>
         <v>7.2</v>
       </c>
-      <c r="H34" s="3">
-        <f t="shared" si="0"/>
+      <c r="H34" s="1">
+        <f t="shared" si="1"/>
         <v>63.157894736842103</v>
       </c>
     </row>
@@ -1444,11 +1444,11 @@
         <v>14</v>
       </c>
       <c r="G35">
-        <f>AVERAGE(B35:F35)</f>
+        <f t="shared" si="0"/>
         <v>8.4</v>
       </c>
-      <c r="H35" s="3">
-        <f t="shared" si="0"/>
+      <c r="H35" s="1">
+        <f t="shared" si="1"/>
         <v>73.68421052631578</v>
       </c>
     </row>
@@ -1472,11 +1472,11 @@
         <v>14</v>
       </c>
       <c r="G36">
-        <f>AVERAGE(B36:F36)</f>
-        <v>8</v>
-      </c>
-      <c r="H36" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="H36" s="1">
+        <f t="shared" si="1"/>
         <v>70.175438596491219</v>
       </c>
     </row>
@@ -1500,11 +1500,11 @@
         <v>1</v>
       </c>
       <c r="G37">
-        <f>AVERAGE(B37:F37)</f>
+        <f t="shared" si="0"/>
         <v>4.8</v>
       </c>
-      <c r="H37" s="3">
-        <f t="shared" si="0"/>
+      <c r="H37" s="1">
+        <f t="shared" si="1"/>
         <v>42.105263157894733</v>
       </c>
     </row>
@@ -1528,11 +1528,11 @@
         <v>1</v>
       </c>
       <c r="G38">
-        <f>AVERAGE(B38:F38)</f>
+        <f t="shared" si="0"/>
         <v>3.4</v>
       </c>
-      <c r="H38" s="3">
-        <f t="shared" si="0"/>
+      <c r="H38" s="1">
+        <f t="shared" si="1"/>
         <v>29.82456140350877</v>
       </c>
     </row>
@@ -1556,11 +1556,11 @@
         <v>1</v>
       </c>
       <c r="G39">
-        <f>AVERAGE(B39:F39)</f>
+        <f t="shared" ref="G39:G70" si="2">AVERAGE(B39:F39)</f>
         <v>3.6</v>
       </c>
-      <c r="H39" s="3">
-        <f t="shared" si="0"/>
+      <c r="H39" s="1">
+        <f t="shared" si="1"/>
         <v>31.578947368421051</v>
       </c>
     </row>
@@ -1584,11 +1584,11 @@
         <v>1</v>
       </c>
       <c r="G40">
-        <f>AVERAGE(B40:F40)</f>
+        <f t="shared" si="2"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="H40" s="3">
-        <f t="shared" si="0"/>
+      <c r="H40" s="1">
+        <f t="shared" si="1"/>
         <v>19.298245614035089</v>
       </c>
     </row>
@@ -1612,11 +1612,11 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <f>AVERAGE(B41:F41)</f>
-        <v>3</v>
-      </c>
-      <c r="H41" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H41" s="1">
+        <f t="shared" si="1"/>
         <v>26.315789473684209</v>
       </c>
     </row>
@@ -1640,11 +1640,11 @@
         <v>14</v>
       </c>
       <c r="G42">
-        <f>AVERAGE(B42:F42)</f>
-        <v>8</v>
-      </c>
-      <c r="H42" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="H42" s="1">
+        <f t="shared" si="1"/>
         <v>70.175438596491219</v>
       </c>
     </row>
@@ -1668,11 +1668,11 @@
         <v>16</v>
       </c>
       <c r="G43">
-        <f>AVERAGE(B43:F43)</f>
+        <f t="shared" si="2"/>
         <v>8.1999999999999993</v>
       </c>
-      <c r="H43" s="3">
-        <f t="shared" si="0"/>
+      <c r="H43" s="1">
+        <f t="shared" si="1"/>
         <v>71.929824561403493</v>
       </c>
     </row>
@@ -1696,11 +1696,11 @@
         <v>13</v>
       </c>
       <c r="G44">
-        <f>AVERAGE(B44:F44)</f>
+        <f t="shared" si="2"/>
         <v>6.8</v>
       </c>
-      <c r="H44" s="3">
-        <f t="shared" si="0"/>
+      <c r="H44" s="1">
+        <f t="shared" si="1"/>
         <v>59.649122807017541</v>
       </c>
     </row>
@@ -1724,11 +1724,11 @@
         <v>1</v>
       </c>
       <c r="G45">
-        <f>AVERAGE(B45:F45)</f>
+        <f t="shared" si="2"/>
         <v>5.8</v>
       </c>
-      <c r="H45" s="3">
-        <f t="shared" si="0"/>
+      <c r="H45" s="1">
+        <f t="shared" si="1"/>
         <v>50.87719298245613</v>
       </c>
     </row>
@@ -1752,11 +1752,11 @@
         <v>14</v>
       </c>
       <c r="G46">
-        <f>AVERAGE(B46:F46)</f>
-        <v>8</v>
-      </c>
-      <c r="H46" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="H46" s="1">
+        <f t="shared" si="1"/>
         <v>70.175438596491219</v>
       </c>
     </row>
@@ -1780,11 +1780,11 @@
         <v>3</v>
       </c>
       <c r="G47">
-        <f>AVERAGE(B47:F47)</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="H47" s="3">
-        <f t="shared" si="0"/>
+      <c r="H47" s="1">
+        <f t="shared" si="1"/>
         <v>52.631578947368418</v>
       </c>
     </row>
@@ -1808,11 +1808,11 @@
         <v>16</v>
       </c>
       <c r="G48">
-        <f>AVERAGE(B48:F48)</f>
+        <f t="shared" si="2"/>
         <v>8.6</v>
       </c>
-      <c r="H48" s="3">
-        <f t="shared" si="0"/>
+      <c r="H48" s="1">
+        <f t="shared" si="1"/>
         <v>75.438596491228054</v>
       </c>
     </row>
@@ -1836,11 +1836,11 @@
         <v>13</v>
       </c>
       <c r="G49">
-        <f>AVERAGE(B49:F49)</f>
+        <f t="shared" si="2"/>
         <v>7.6</v>
       </c>
-      <c r="H49" s="3">
-        <f t="shared" si="0"/>
+      <c r="H49" s="1">
+        <f t="shared" si="1"/>
         <v>66.666666666666657</v>
       </c>
     </row>
@@ -1864,11 +1864,11 @@
         <v>16</v>
       </c>
       <c r="G50">
-        <f>AVERAGE(B50:F50)</f>
+        <f t="shared" si="2"/>
         <v>9.1999999999999993</v>
       </c>
-      <c r="H50" s="3">
-        <f t="shared" si="0"/>
+      <c r="H50" s="1">
+        <f t="shared" si="1"/>
         <v>80.701754385964904</v>
       </c>
     </row>
@@ -1892,11 +1892,11 @@
         <v>13</v>
       </c>
       <c r="G51">
-        <f>AVERAGE(B51:F51)</f>
+        <f t="shared" si="2"/>
         <v>8.4</v>
       </c>
-      <c r="H51" s="3">
-        <f t="shared" si="0"/>
+      <c r="H51" s="1">
+        <f t="shared" si="1"/>
         <v>73.68421052631578</v>
       </c>
     </row>
@@ -1920,11 +1920,11 @@
         <v>19</v>
       </c>
       <c r="G52">
-        <f>AVERAGE(B52:F52)</f>
+        <f t="shared" si="2"/>
         <v>8.8000000000000007</v>
       </c>
-      <c r="H52" s="3">
-        <f t="shared" si="0"/>
+      <c r="H52" s="1">
+        <f t="shared" si="1"/>
         <v>77.192982456140356</v>
       </c>
     </row>
@@ -1948,11 +1948,11 @@
         <v>14</v>
       </c>
       <c r="G53">
-        <f>AVERAGE(B53:F53)</f>
-        <v>8</v>
-      </c>
-      <c r="H53" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="H53" s="1">
+        <f t="shared" si="1"/>
         <v>70.175438596491219</v>
       </c>
     </row>
@@ -1976,11 +1976,11 @@
         <v>14</v>
       </c>
       <c r="G54">
-        <f>AVERAGE(B54:F54)</f>
+        <f t="shared" si="2"/>
         <v>8.4</v>
       </c>
-      <c r="H54" s="3">
-        <f t="shared" si="0"/>
+      <c r="H54" s="1">
+        <f t="shared" si="1"/>
         <v>73.68421052631578</v>
       </c>
     </row>
@@ -2004,11 +2004,11 @@
         <v>15</v>
       </c>
       <c r="G55">
-        <f>AVERAGE(B55:F55)</f>
+        <f t="shared" si="2"/>
         <v>8.4</v>
       </c>
-      <c r="H55" s="3">
-        <f t="shared" si="0"/>
+      <c r="H55" s="1">
+        <f t="shared" si="1"/>
         <v>73.68421052631578</v>
       </c>
     </row>
@@ -2032,11 +2032,11 @@
         <v>15</v>
       </c>
       <c r="G56">
-        <f>AVERAGE(B56:F56)</f>
+        <f t="shared" si="2"/>
         <v>7.2</v>
       </c>
-      <c r="H56" s="3">
-        <f t="shared" si="0"/>
+      <c r="H56" s="1">
+        <f t="shared" si="1"/>
         <v>63.157894736842103</v>
       </c>
     </row>
@@ -2060,11 +2060,11 @@
         <v>13</v>
       </c>
       <c r="G57">
-        <f>AVERAGE(B57:F57)</f>
+        <f t="shared" si="2"/>
         <v>7.8</v>
       </c>
-      <c r="H57" s="3">
-        <f t="shared" si="0"/>
+      <c r="H57" s="1">
+        <f t="shared" si="1"/>
         <v>68.421052631578945</v>
       </c>
     </row>
@@ -2088,11 +2088,11 @@
         <v>13</v>
       </c>
       <c r="G58">
-        <f>AVERAGE(B58:F58)</f>
+        <f t="shared" si="2"/>
         <v>7.4</v>
       </c>
-      <c r="H58" s="3">
-        <f t="shared" si="0"/>
+      <c r="H58" s="1">
+        <f t="shared" si="1"/>
         <v>64.912280701754383</v>
       </c>
     </row>
@@ -2116,11 +2116,11 @@
         <v>13</v>
       </c>
       <c r="G59">
-        <f>AVERAGE(B59:F59)</f>
+        <f t="shared" si="2"/>
         <v>7.8</v>
       </c>
-      <c r="H59" s="3">
-        <f t="shared" si="0"/>
+      <c r="H59" s="1">
+        <f t="shared" si="1"/>
         <v>68.421052631578945</v>
       </c>
     </row>
@@ -2144,11 +2144,11 @@
         <v>15</v>
       </c>
       <c r="G60">
-        <f>AVERAGE(B60:F60)</f>
+        <f t="shared" si="2"/>
         <v>8.1999999999999993</v>
       </c>
-      <c r="H60" s="3">
-        <f t="shared" si="0"/>
+      <c r="H60" s="1">
+        <f t="shared" si="1"/>
         <v>71.929824561403493</v>
       </c>
     </row>
@@ -2172,11 +2172,11 @@
         <v>20</v>
       </c>
       <c r="G61">
-        <f>AVERAGE(B61:F61)</f>
+        <f t="shared" si="2"/>
         <v>9.6</v>
       </c>
-      <c r="H61" s="3">
-        <f t="shared" si="0"/>
+      <c r="H61" s="1">
+        <f t="shared" si="1"/>
         <v>84.210526315789465</v>
       </c>
     </row>
@@ -2200,11 +2200,11 @@
         <v>20</v>
       </c>
       <c r="G62">
-        <f>AVERAGE(B62:F62)</f>
+        <f t="shared" si="2"/>
         <v>10.4</v>
       </c>
-      <c r="H62" s="3">
-        <f t="shared" si="0"/>
+      <c r="H62" s="1">
+        <f t="shared" si="1"/>
         <v>91.228070175438589</v>
       </c>
     </row>
@@ -2228,11 +2228,11 @@
         <v>19</v>
       </c>
       <c r="G63">
-        <f>AVERAGE(B63:F63)</f>
+        <f t="shared" si="2"/>
         <v>10.199999999999999</v>
       </c>
-      <c r="H63" s="3">
-        <f t="shared" si="0"/>
+      <c r="H63" s="1">
+        <f t="shared" si="1"/>
         <v>89.473684210526301</v>
       </c>
     </row>
@@ -2256,17 +2256,17 @@
         <v>19</v>
       </c>
       <c r="G64">
-        <f>AVERAGE(B64:F64)</f>
+        <f t="shared" si="2"/>
         <v>10.4</v>
       </c>
-      <c r="H64" s="3">
-        <f t="shared" si="0"/>
+      <c r="H64" s="1">
+        <f t="shared" si="1"/>
         <v>91.228070175438589</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B65">
         <v>10</v>
@@ -2284,11 +2284,11 @@
         <v>20</v>
       </c>
       <c r="G65">
-        <f>AVERAGE(B65:F65)</f>
+        <f t="shared" si="2"/>
         <v>11.4</v>
       </c>
-      <c r="H65" s="3">
-        <f t="shared" si="0"/>
+      <c r="H65" s="1">
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
     </row>
